--- a/evac_by_zip/evac_by_zip_2026-08-14.xlsx
+++ b/evac_by_zip/evac_by_zip_2026-08-14.xlsx
@@ -578,7 +578,7 @@
     <row r="2" ht="42" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Address counts estimated via area-weighted polygon intersection of OEM evac zones × Census ZCTA boundaries. Source: Oregon OEM Fire_Evacuation_Areas_Public + Census TIGERweb ZCTA. NOTE: 290 addresses (across 0 zones) could not be placed on a ZIP code this run and are NOT included in the totals below — see the summary rows at the bottom of this table and the Evacuation Map's 'Unmatched zones' layer for detail.</t>
+          <t>Address counts estimated via area-weighted polygon intersection of OEM evac zones × Census ZCTA boundaries. Source: Oregon OEM Fire_Evacuation_Areas_Public + Census TIGERweb ZCTA. NOTE: 302 addresses (across 2 zones) could not be placed on a ZIP code this run and are NOT included in the totals below — see the summary rows at the bottom of this table and the Evacuation Map's 'Unmatched zones' layer for detail.</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Fielders Mountain</t>
         </is>
       </c>
     </row>
@@ -729,7 +729,7 @@
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Fielders Mountain</t>
         </is>
       </c>
     </row>
@@ -740,13 +740,13 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="E7" s="4" t="n">
         <v>667</v>
@@ -845,13 +845,13 @@
         <v>130</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
@@ -876,16 +876,16 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
@@ -944,16 +944,16 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>87</v>
+        <v>111</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>81</v>
+        <v>43</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
@@ -1040,83 +1040,87 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>97621</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="n">
-        <v>49</v>
-      </c>
-      <c r="C16" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="D16" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E16" s="4" t="n">
-        <v>64</v>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>97625</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="C16" s="8" t="n">
+        <v>35</v>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>55</v>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>Level 2</t>
+        </is>
+      </c>
+      <c r="G16" s="9" t="inlineStr">
+        <is>
+          <t>Klamath</t>
+        </is>
+      </c>
+      <c r="H16" s="9" t="inlineStr">
+        <is>
+          <t>Wrights Spring</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>97827</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>Level 3</t>
         </is>
       </c>
-      <c r="G16" s="6" t="inlineStr">
-        <is>
-          <t>Klamath</t>
-        </is>
-      </c>
-      <c r="H16" s="6" t="inlineStr">
-        <is>
-          <t>Wrights Spring</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>97625</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="C17" s="8" t="n">
-        <v>35</v>
-      </c>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E17" s="7" t="n">
-        <v>55</v>
-      </c>
-      <c r="F17" s="7" t="inlineStr">
-        <is>
-          <t>Level 2</t>
-        </is>
-      </c>
-      <c r="G17" s="9" t="inlineStr">
-        <is>
-          <t>Klamath</t>
-        </is>
-      </c>
-      <c r="H17" s="9" t="inlineStr">
-        <is>
-          <t>Wrights Spring</t>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>Umatilla, Union</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>No named fire</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>97827</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="n">
-        <v>1</v>
+          <t>97862</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
@@ -1124,10 +1128,10 @@
         </is>
       </c>
       <c r="D18" s="5" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
@@ -1136,7 +1140,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>Umatilla, Union</t>
+          <t>Umatilla</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
@@ -1148,164 +1152,162 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>97862</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
+          <t>97023</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="D19" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>Level 3</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>Clackamas</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>97859</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D19" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="E19" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>Level 3</t>
-        </is>
-      </c>
-      <c r="G19" s="6" t="inlineStr">
+      <c r="C20" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>Level 2</t>
+        </is>
+      </c>
+      <c r="G20" s="9" t="inlineStr">
         <is>
           <t>Umatilla</t>
         </is>
       </c>
-      <c r="H19" s="6" t="inlineStr">
+      <c r="H20" s="9" t="inlineStr">
         <is>
           <t>No named fire</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>97023</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>97028</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="n">
+        <v>836</v>
+      </c>
+      <c r="C21" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D20" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E20" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>Level 3</t>
-        </is>
-      </c>
-      <c r="G20" s="6" t="inlineStr">
-        <is>
-          <t>Clackamas</t>
-        </is>
-      </c>
-      <c r="H20" s="6" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>97859</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="D21" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C21" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" s="8" t="inlineStr">
+      <c r="E21" s="10" t="n">
+        <v>836</v>
+      </c>
+      <c r="F21" s="10" t="inlineStr">
+        <is>
+          <t>Level 1</t>
+        </is>
+      </c>
+      <c r="G21" s="12" t="inlineStr">
+        <is>
+          <t>Clackamas, Hood River</t>
+        </is>
+      </c>
+      <c r="H21" s="12" t="inlineStr">
+        <is>
+          <t>Grasshopper</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>97750</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="n">
+        <v>169</v>
+      </c>
+      <c r="C22" s="8" t="n">
+        <v>79</v>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E21" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F21" s="7" t="inlineStr">
+      <c r="E22" s="7" t="n">
+        <v>248</v>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
         <is>
           <t>Level 2</t>
         </is>
       </c>
-      <c r="G21" s="9" t="inlineStr">
-        <is>
-          <t>Umatilla</t>
-        </is>
-      </c>
-      <c r="H21" s="9" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="10" t="inlineStr">
-        <is>
-          <t>97028</t>
-        </is>
-      </c>
-      <c r="B22" s="11" t="n">
-        <v>836</v>
-      </c>
-      <c r="C22" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D22" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E22" s="10" t="n">
-        <v>836</v>
-      </c>
-      <c r="F22" s="10" t="inlineStr">
-        <is>
-          <t>Level 1</t>
-        </is>
-      </c>
-      <c r="G22" s="12" t="inlineStr">
-        <is>
-          <t>Clackamas, Hood River</t>
-        </is>
-      </c>
-      <c r="H22" s="12" t="inlineStr">
-        <is>
-          <t>Grasshopper</t>
+      <c r="G22" s="9" t="inlineStr">
+        <is>
+          <t>Grant, Wheeler</t>
+        </is>
+      </c>
+      <c r="H22" s="9" t="inlineStr">
+        <is>
+          <t>No named fire; Rowe Creek Complex; Shingle</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>97750</t>
+          <t>97876</t>
         </is>
       </c>
       <c r="B23" s="8" t="n">
-        <v>169</v>
+        <v>61</v>
       </c>
       <c r="C23" s="8" t="n">
-        <v>79</v>
+        <v>7</v>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
@@ -1313,7 +1315,7 @@
         </is>
       </c>
       <c r="E23" s="7" t="n">
-        <v>248</v>
+        <v>68</v>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
@@ -1322,26 +1324,26 @@
       </c>
       <c r="G23" s="9" t="inlineStr">
         <is>
-          <t>Grant, Wheeler</t>
+          <t>Union</t>
         </is>
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
-          <t>No named fire; Rowe Creek Complex; Shingle</t>
+          <t>No named fire</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>97876</t>
+          <t>97621</t>
         </is>
       </c>
       <c r="B24" s="8" t="n">
         <v>61</v>
       </c>
       <c r="C24" s="8" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
@@ -1349,7 +1351,7 @@
         </is>
       </c>
       <c r="E24" s="7" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
@@ -1358,12 +1360,12 @@
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
-          <t>Union</t>
+          <t>Klamath</t>
         </is>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Wrights Spring</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2077,7 @@
       </c>
       <c r="H43" s="12" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Fielders Mountain</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2153,7 @@
       </c>
       <c r="H45" s="12" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Fielders Mountain</t>
         </is>
       </c>
     </row>
@@ -2200,16 +2202,16 @@
         </is>
       </c>
       <c r="B48" s="14" t="n">
-        <v>4279</v>
+        <v>4306</v>
       </c>
       <c r="C48" s="14" t="n">
-        <v>2859</v>
+        <v>2890</v>
       </c>
       <c r="D48" s="14" t="n">
-        <v>1871</v>
+        <v>1801</v>
       </c>
       <c r="E48" s="14" t="n">
-        <v>9009</v>
+        <v>8997</v>
       </c>
     </row>
     <row r="49">
@@ -2219,16 +2221,16 @@
         </is>
       </c>
       <c r="B49" s="16" t="n">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C49" s="16" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D49" s="16" t="n">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="E49" s="16" t="n">
-        <v>290</v>
+        <v>302</v>
       </c>
     </row>
     <row r="50">
@@ -2238,13 +2240,13 @@
         </is>
       </c>
       <c r="B50" s="18" t="n">
-        <v>4458</v>
+        <v>4489</v>
       </c>
       <c r="C50" s="18" t="n">
-        <v>2918</v>
+        <v>2948</v>
       </c>
       <c r="D50" s="18" t="n">
-        <v>1923</v>
+        <v>1862</v>
       </c>
       <c r="E50" s="18" t="n">
         <v>9299</v>
@@ -2789,7 +2791,7 @@
       </c>
       <c r="C16" s="22" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Fielders Mountain</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -2824,7 +2826,7 @@
       </c>
       <c r="C17" s="22" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Fielders Mountain</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -2859,7 +2861,7 @@
       </c>
       <c r="C18" s="22" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Fielders Mountain</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -2894,7 +2896,7 @@
       </c>
       <c r="C19" s="24" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Fielders Mountain</t>
         </is>
       </c>
       <c r="D19" s="24" t="inlineStr">
@@ -2929,7 +2931,7 @@
       </c>
       <c r="C20" s="26" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Fielders Mountain</t>
         </is>
       </c>
       <c r="D20" s="26" t="inlineStr">
@@ -2964,7 +2966,7 @@
       </c>
       <c r="C21" s="26" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Fielders Mountain</t>
         </is>
       </c>
       <c r="D21" s="26" t="inlineStr">
@@ -2999,7 +3001,7 @@
       </c>
       <c r="C22" s="26" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Fielders Mountain</t>
         </is>
       </c>
       <c r="D22" s="26" t="inlineStr">
@@ -3034,7 +3036,7 @@
       </c>
       <c r="C23" s="26" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Fielders Mountain</t>
         </is>
       </c>
       <c r="D23" s="26" t="inlineStr">
@@ -3069,7 +3071,7 @@
       </c>
       <c r="C24" s="26" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Fielders Mountain</t>
         </is>
       </c>
       <c r="D24" s="26" t="inlineStr">
@@ -3104,7 +3106,7 @@
       </c>
       <c r="C25" s="26" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Fielders Mountain</t>
         </is>
       </c>
       <c r="D25" s="26" t="inlineStr">
@@ -3139,7 +3141,7 @@
       </c>
       <c r="C26" s="22" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Fielders Mountain</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -3174,7 +3176,7 @@
       </c>
       <c r="C27" s="22" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Fielders Mountain</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -3209,7 +3211,7 @@
       </c>
       <c r="C28" s="24" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Fielders Mountain</t>
         </is>
       </c>
       <c r="D28" s="24" t="inlineStr">
@@ -3244,7 +3246,7 @@
       </c>
       <c r="C29" s="26" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Fielders Mountain</t>
         </is>
       </c>
       <c r="D29" s="26" t="inlineStr">
@@ -3279,7 +3281,7 @@
       </c>
       <c r="C30" s="26" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Fielders Mountain</t>
         </is>
       </c>
       <c r="D30" s="26" t="inlineStr">
@@ -3314,7 +3316,7 @@
       </c>
       <c r="C31" s="26" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Fielders Mountain</t>
         </is>
       </c>
       <c r="D31" s="26" t="inlineStr">
@@ -3484,7 +3486,7 @@
       </c>
       <c r="B36" s="22" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1566</t>
+          <t>US-OR-KLA-KLA-1713-A</t>
         </is>
       </c>
       <c r="C36" s="22" t="inlineStr">
@@ -3504,11 +3506,11 @@
       </c>
       <c r="F36" s="21" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G36" s="21" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
@@ -3519,7 +3521,7 @@
       </c>
       <c r="B37" s="22" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1713-A</t>
+          <t>US-OR-KLA-KLA-1713-B</t>
         </is>
       </c>
       <c r="C37" s="22" t="inlineStr">
@@ -3539,151 +3541,151 @@
       </c>
       <c r="F37" s="21" t="inlineStr">
         <is>
+          <t>98%</t>
+        </is>
+      </c>
+      <c r="G37" s="21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="23" t="inlineStr">
+        <is>
+          <t>97623</t>
+        </is>
+      </c>
+      <c r="B38" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-KLA-KLA-1968</t>
+        </is>
+      </c>
+      <c r="C38" s="24" t="inlineStr">
+        <is>
+          <t>Wrights Spring</t>
+        </is>
+      </c>
+      <c r="D38" s="24" t="inlineStr">
+        <is>
+          <t>Klamath</t>
+        </is>
+      </c>
+      <c r="E38" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F38" s="23" t="inlineStr">
+        <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="G37" s="21" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="21" t="inlineStr">
+      <c r="G38" s="23" t="n">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="23" t="inlineStr">
         <is>
           <t>97623</t>
         </is>
       </c>
-      <c r="B38" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-KLA-1572</t>
-        </is>
-      </c>
-      <c r="C38" s="22" t="inlineStr">
+      <c r="B39" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-KLA-KLA-1967</t>
+        </is>
+      </c>
+      <c r="C39" s="24" t="inlineStr">
         <is>
           <t>Wrights Spring</t>
         </is>
       </c>
-      <c r="D38" s="22" t="inlineStr">
+      <c r="D39" s="24" t="inlineStr">
         <is>
           <t>Klamath</t>
         </is>
       </c>
-      <c r="E38" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F38" s="21" t="inlineStr">
-        <is>
-          <t>51%</t>
-        </is>
-      </c>
-      <c r="G38" s="21" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="21" t="inlineStr">
+      <c r="E39" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F39" s="23" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G39" s="23" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="23" t="inlineStr">
         <is>
           <t>97623</t>
         </is>
       </c>
-      <c r="B39" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-KLA-1718-B</t>
-        </is>
-      </c>
-      <c r="C39" s="22" t="inlineStr">
+      <c r="B40" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-KLA-KLA-1721</t>
+        </is>
+      </c>
+      <c r="C40" s="24" t="inlineStr">
         <is>
           <t>Wrights Spring</t>
         </is>
       </c>
-      <c r="D39" s="22" t="inlineStr">
+      <c r="D40" s="24" t="inlineStr">
         <is>
           <t>Klamath</t>
         </is>
       </c>
-      <c r="E39" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F39" s="21" t="inlineStr">
-        <is>
-          <t>98%</t>
-        </is>
-      </c>
-      <c r="G39" s="21" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="21" t="inlineStr">
+      <c r="E40" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F40" s="23" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G40" s="23" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="23" t="inlineStr">
         <is>
           <t>97623</t>
         </is>
       </c>
-      <c r="B40" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-KLA-1718-A</t>
-        </is>
-      </c>
-      <c r="C40" s="22" t="inlineStr">
+      <c r="B41" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-KLA-KLA-1972</t>
+        </is>
+      </c>
+      <c r="C41" s="24" t="inlineStr">
         <is>
           <t>Wrights Spring</t>
         </is>
       </c>
-      <c r="D40" s="22" t="inlineStr">
+      <c r="D41" s="24" t="inlineStr">
         <is>
           <t>Klamath</t>
         </is>
       </c>
-      <c r="E40" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F40" s="21" t="inlineStr">
-        <is>
-          <t>62%</t>
-        </is>
-      </c>
-      <c r="G40" s="21" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="21" t="inlineStr">
-        <is>
-          <t>97623</t>
-        </is>
-      </c>
-      <c r="B41" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-KLA-1713-B</t>
-        </is>
-      </c>
-      <c r="C41" s="22" t="inlineStr">
-        <is>
-          <t>Wrights Spring</t>
-        </is>
-      </c>
-      <c r="D41" s="22" t="inlineStr">
-        <is>
-          <t>Klamath</t>
-        </is>
-      </c>
-      <c r="E41" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F41" s="21" t="inlineStr">
-        <is>
-          <t>98%</t>
-        </is>
-      </c>
-      <c r="G41" s="21" t="n">
-        <v>1</v>
+      <c r="E41" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F41" s="23" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G41" s="23" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="42">
@@ -3694,7 +3696,7 @@
       </c>
       <c r="B42" s="24" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1968</t>
+          <t>US-OR-KLA-KLA-1722</t>
         </is>
       </c>
       <c r="C42" s="24" t="inlineStr">
@@ -3718,7 +3720,7 @@
         </is>
       </c>
       <c r="G42" s="23" t="n">
-        <v>139</v>
+        <v>28</v>
       </c>
     </row>
     <row r="43">
@@ -3729,7 +3731,7 @@
       </c>
       <c r="B43" s="24" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1967</t>
+          <t>US-OR-KLA-KLA-1719-B</t>
         </is>
       </c>
       <c r="C43" s="24" t="inlineStr">
@@ -3753,7 +3755,7 @@
         </is>
       </c>
       <c r="G43" s="23" t="n">
-        <v>58</v>
+        <v>24</v>
       </c>
     </row>
     <row r="44">
@@ -3764,7 +3766,7 @@
       </c>
       <c r="B44" s="24" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1721</t>
+          <t>US-OR-KLA-KLA-1727</t>
         </is>
       </c>
       <c r="C44" s="24" t="inlineStr">
@@ -3788,7 +3790,7 @@
         </is>
       </c>
       <c r="G44" s="23" t="n">
-        <v>49</v>
+        <v>16</v>
       </c>
     </row>
     <row r="45">
@@ -3799,7 +3801,7 @@
       </c>
       <c r="B45" s="24" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1972</t>
+          <t>US-OR-KLA-KLA-1731</t>
         </is>
       </c>
       <c r="C45" s="24" t="inlineStr">
@@ -3823,7 +3825,7 @@
         </is>
       </c>
       <c r="G45" s="23" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
     </row>
     <row r="46">
@@ -3834,7 +3836,7 @@
       </c>
       <c r="B46" s="24" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1722</t>
+          <t>US-OR-KLA-KLA-1957-A</t>
         </is>
       </c>
       <c r="C46" s="24" t="inlineStr">
@@ -3858,7 +3860,7 @@
         </is>
       </c>
       <c r="G46" s="23" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
     </row>
     <row r="47">
@@ -3869,7 +3871,7 @@
       </c>
       <c r="B47" s="24" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1719-B</t>
+          <t>US-OR-KLA-KLA-1736-A</t>
         </is>
       </c>
       <c r="C47" s="24" t="inlineStr">
@@ -3893,7 +3895,7 @@
         </is>
       </c>
       <c r="G47" s="23" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
     </row>
     <row r="48">
@@ -3904,7 +3906,7 @@
       </c>
       <c r="B48" s="24" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1727</t>
+          <t>US-OR-KLA-KLA-1976</t>
         </is>
       </c>
       <c r="C48" s="24" t="inlineStr">
@@ -3924,11 +3926,11 @@
       </c>
       <c r="F48" s="23" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>72%</t>
         </is>
       </c>
       <c r="G48" s="23" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="49">
@@ -3939,7 +3941,7 @@
       </c>
       <c r="B49" s="24" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1731</t>
+          <t>US-OR-KLA-KLA-1726</t>
         </is>
       </c>
       <c r="C49" s="24" t="inlineStr">
@@ -3963,7 +3965,7 @@
         </is>
       </c>
       <c r="G49" s="23" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="50">
@@ -3974,7 +3976,7 @@
       </c>
       <c r="B50" s="24" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1957-A</t>
+          <t>US-OR-KLA-KLA-1956</t>
         </is>
       </c>
       <c r="C50" s="24" t="inlineStr">
@@ -3998,7 +4000,7 @@
         </is>
       </c>
       <c r="G50" s="23" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="51">
@@ -4009,7 +4011,7 @@
       </c>
       <c r="B51" s="24" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1736-A</t>
+          <t>US-OR-KLA-KLA-1566</t>
         </is>
       </c>
       <c r="C51" s="24" t="inlineStr">
@@ -4029,11 +4031,11 @@
       </c>
       <c r="F51" s="23" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>37%</t>
         </is>
       </c>
       <c r="G51" s="23" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="52">
@@ -4044,7 +4046,7 @@
       </c>
       <c r="B52" s="24" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1976</t>
+          <t>US-OR-KLA-KLA-1707</t>
         </is>
       </c>
       <c r="C52" s="24" t="inlineStr">
@@ -4064,11 +4066,11 @@
       </c>
       <c r="F52" s="23" t="inlineStr">
         <is>
-          <t>72%</t>
+          <t>16%</t>
         </is>
       </c>
       <c r="G52" s="23" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="53">
@@ -4079,7 +4081,7 @@
       </c>
       <c r="B53" s="24" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1726</t>
+          <t>US-OR-KLA-KLA-1572</t>
         </is>
       </c>
       <c r="C53" s="24" t="inlineStr">
@@ -4099,11 +4101,11 @@
       </c>
       <c r="F53" s="23" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>51%</t>
         </is>
       </c>
       <c r="G53" s="23" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54">
@@ -4114,7 +4116,7 @@
       </c>
       <c r="B54" s="24" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1956</t>
+          <t>US-OR-KLA-KLA-1718-B</t>
         </is>
       </c>
       <c r="C54" s="24" t="inlineStr">
@@ -4134,11 +4136,11 @@
       </c>
       <c r="F54" s="23" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>98%</t>
         </is>
       </c>
       <c r="G54" s="23" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -4149,7 +4151,7 @@
       </c>
       <c r="B55" s="24" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1707</t>
+          <t>US-OR-KLA-KLA-1718-A</t>
         </is>
       </c>
       <c r="C55" s="24" t="inlineStr">
@@ -4169,81 +4171,81 @@
       </c>
       <c r="F55" s="23" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>62%</t>
         </is>
       </c>
       <c r="G55" s="23" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="23" t="inlineStr">
+      <c r="A56" s="25" t="inlineStr">
         <is>
           <t>97623</t>
         </is>
       </c>
-      <c r="B56" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-KLA-1737</t>
-        </is>
-      </c>
-      <c r="C56" s="24" t="inlineStr">
+      <c r="B56" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-KLA-KLA-1971</t>
+        </is>
+      </c>
+      <c r="C56" s="26" t="inlineStr">
         <is>
           <t>Wrights Spring</t>
         </is>
       </c>
-      <c r="D56" s="24" t="inlineStr">
+      <c r="D56" s="26" t="inlineStr">
         <is>
           <t>Klamath</t>
         </is>
       </c>
-      <c r="E56" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F56" s="23" t="inlineStr">
-        <is>
-          <t>44%</t>
-        </is>
-      </c>
-      <c r="G56" s="23" t="n">
-        <v>3</v>
+      <c r="E56" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F56" s="25" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G56" s="25" t="n">
+        <v>58</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="23" t="inlineStr">
+      <c r="A57" s="25" t="inlineStr">
         <is>
           <t>97623</t>
         </is>
       </c>
-      <c r="B57" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-KLA-1472</t>
-        </is>
-      </c>
-      <c r="C57" s="24" t="inlineStr">
+      <c r="B57" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-KLA-KLA-2291</t>
+        </is>
+      </c>
+      <c r="C57" s="26" t="inlineStr">
         <is>
           <t>Wrights Spring</t>
         </is>
       </c>
-      <c r="D57" s="24" t="inlineStr">
+      <c r="D57" s="26" t="inlineStr">
         <is>
           <t>Klamath</t>
         </is>
       </c>
-      <c r="E57" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F57" s="23" t="inlineStr">
-        <is>
-          <t>7%</t>
-        </is>
-      </c>
-      <c r="G57" s="23" t="n">
-        <v>1</v>
+      <c r="E57" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F57" s="25" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G57" s="25" t="n">
+        <v>48</v>
       </c>
     </row>
     <row r="58">
@@ -4254,7 +4256,7 @@
       </c>
       <c r="B58" s="26" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1971</t>
+          <t>US-OR-KLA-KLA-1961</t>
         </is>
       </c>
       <c r="C58" s="26" t="inlineStr">
@@ -4278,7 +4280,7 @@
         </is>
       </c>
       <c r="G58" s="25" t="n">
-        <v>58</v>
+        <v>34</v>
       </c>
     </row>
     <row r="59">
@@ -4289,7 +4291,7 @@
       </c>
       <c r="B59" s="26" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-2291</t>
+          <t>US-OR-KLA-KLA-1946</t>
         </is>
       </c>
       <c r="C59" s="26" t="inlineStr">
@@ -4309,11 +4311,11 @@
       </c>
       <c r="F59" s="25" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="G59" s="25" t="n">
-        <v>48</v>
+        <v>16</v>
       </c>
     </row>
     <row r="60">
@@ -4324,7 +4326,7 @@
       </c>
       <c r="B60" s="26" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1961</t>
+          <t>US-OR-KLA-KLA-1951</t>
         </is>
       </c>
       <c r="C60" s="26" t="inlineStr">
@@ -4348,7 +4350,7 @@
         </is>
       </c>
       <c r="G60" s="25" t="n">
-        <v>34</v>
+        <v>15</v>
       </c>
     </row>
     <row r="61">
@@ -4359,7 +4361,7 @@
       </c>
       <c r="B61" s="26" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1946</t>
+          <t>US-OR-KLA-KLA-1737</t>
         </is>
       </c>
       <c r="C61" s="26" t="inlineStr">
@@ -4379,11 +4381,11 @@
       </c>
       <c r="F61" s="25" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>44%</t>
         </is>
       </c>
       <c r="G61" s="25" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="62">
@@ -4394,7 +4396,7 @@
       </c>
       <c r="B62" s="26" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1951</t>
+          <t>US-OR-KLA-KLA-1966</t>
         </is>
       </c>
       <c r="C62" s="26" t="inlineStr">
@@ -4418,7 +4420,7 @@
         </is>
       </c>
       <c r="G62" s="25" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4429,7 +4431,7 @@
       </c>
       <c r="B63" s="26" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1966</t>
+          <t>US-OR-KLA-KLA-2296</t>
         </is>
       </c>
       <c r="C63" s="26" t="inlineStr">
@@ -4464,7 +4466,7 @@
       </c>
       <c r="B64" s="26" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-2296</t>
+          <t>US-OR-KLA-KLA-1472</t>
         </is>
       </c>
       <c r="C64" s="26" t="inlineStr">
@@ -4484,7 +4486,7 @@
       </c>
       <c r="F64" s="25" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="G64" s="25" t="n">
@@ -6343,7 +6345,7 @@
         </is>
       </c>
       <c r="G117" s="21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="118">
@@ -6354,7 +6356,7 @@
       </c>
       <c r="B118" s="22" t="inlineStr">
         <is>
-          <t>US-OR-CRO-CRR-4SB-J</t>
+          <t>US-OR-CRO-CRR-4SB-G</t>
         </is>
       </c>
       <c r="C118" s="22" t="inlineStr">
@@ -6374,11 +6376,11 @@
       </c>
       <c r="F118" s="21" t="inlineStr">
         <is>
-          <t>99%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G118" s="21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="119">
@@ -6389,7 +6391,7 @@
       </c>
       <c r="B119" s="22" t="inlineStr">
         <is>
-          <t>US-OR-CRO-CRR-4SB-G</t>
+          <t>US-OR-CRO-CRR-4SK-A</t>
         </is>
       </c>
       <c r="C119" s="22" t="inlineStr">
@@ -6413,7 +6415,7 @@
         </is>
       </c>
       <c r="G119" s="21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="120">
@@ -6424,7 +6426,7 @@
       </c>
       <c r="B120" s="22" t="inlineStr">
         <is>
-          <t>US-OR-CRO-CRR-4SK-A</t>
+          <t>US-OR-CRO-CRR-4S-I</t>
         </is>
       </c>
       <c r="C120" s="22" t="inlineStr">
@@ -6459,7 +6461,7 @@
       </c>
       <c r="B121" s="22" t="inlineStr">
         <is>
-          <t>US-OR-CRO-CRR-4S-I</t>
+          <t>US-OR-CRO-CRR-4SK-B</t>
         </is>
       </c>
       <c r="C121" s="22" t="inlineStr">
@@ -6483,7 +6485,7 @@
         </is>
       </c>
       <c r="G121" s="21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="122">
@@ -6494,7 +6496,7 @@
       </c>
       <c r="B122" s="22" t="inlineStr">
         <is>
-          <t>US-OR-CRO-CRR-4SK-B</t>
+          <t>US-OR-CRO-CRR-8S-M</t>
         </is>
       </c>
       <c r="C122" s="22" t="inlineStr">
@@ -6514,7 +6516,7 @@
       </c>
       <c r="F122" s="21" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="G122" s="21" t="n">
@@ -6529,7 +6531,7 @@
       </c>
       <c r="B123" s="22" t="inlineStr">
         <is>
-          <t>US-OR-CRO-CRR-1S-Q</t>
+          <t>US-OR-CRO-CRR-8S-I</t>
         </is>
       </c>
       <c r="C123" s="22" t="inlineStr">
@@ -6549,7 +6551,7 @@
       </c>
       <c r="F123" s="21" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G123" s="21" t="n">
@@ -6564,7 +6566,7 @@
       </c>
       <c r="B124" s="22" t="inlineStr">
         <is>
-          <t>US-OR-CRO-CRR-8S-M</t>
+          <t>US-OR-CRO-CRR-4S-E</t>
         </is>
       </c>
       <c r="C124" s="22" t="inlineStr">
@@ -6584,7 +6586,7 @@
       </c>
       <c r="F124" s="21" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G124" s="21" t="n">
@@ -6592,73 +6594,73 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="21" t="inlineStr">
+      <c r="A125" s="23" t="inlineStr">
         <is>
           <t>97754</t>
         </is>
       </c>
-      <c r="B125" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-CRO-CRR-8S-I</t>
-        </is>
-      </c>
-      <c r="C125" s="22" t="inlineStr">
+      <c r="B125" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-CRO-CRR-4S-D</t>
+        </is>
+      </c>
+      <c r="C125" s="24" t="inlineStr">
         <is>
           <t>Rowe Creek Complex</t>
         </is>
       </c>
-      <c r="D125" s="22" t="inlineStr">
+      <c r="D125" s="24" t="inlineStr">
         <is>
           <t>Crook, Wheeler</t>
         </is>
       </c>
-      <c r="E125" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F125" s="21" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G125" s="21" t="n">
-        <v>1</v>
+      <c r="E125" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F125" s="23" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G125" s="23" t="n">
+        <v>62</v>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="21" t="inlineStr">
+      <c r="A126" s="23" t="inlineStr">
         <is>
           <t>97754</t>
         </is>
       </c>
-      <c r="B126" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-CRO-CRR-4S-E</t>
-        </is>
-      </c>
-      <c r="C126" s="22" t="inlineStr">
+      <c r="B126" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-CRO-CRR-8S-F</t>
+        </is>
+      </c>
+      <c r="C126" s="24" t="inlineStr">
         <is>
           <t>Rowe Creek Complex</t>
         </is>
       </c>
-      <c r="D126" s="22" t="inlineStr">
+      <c r="D126" s="24" t="inlineStr">
         <is>
           <t>Crook, Wheeler</t>
         </is>
       </c>
-      <c r="E126" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F126" s="21" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G126" s="21" t="n">
-        <v>1</v>
+      <c r="E126" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F126" s="23" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G126" s="23" t="n">
+        <v>53</v>
       </c>
     </row>
     <row r="127">
@@ -6669,7 +6671,7 @@
       </c>
       <c r="B127" s="24" t="inlineStr">
         <is>
-          <t>US-OR-CRO-CRR-4S-D</t>
+          <t>US-OR-CRO-CRR-8S-O</t>
         </is>
       </c>
       <c r="C127" s="24" t="inlineStr">
@@ -6689,11 +6691,11 @@
       </c>
       <c r="F127" s="23" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>83%</t>
         </is>
       </c>
       <c r="G127" s="23" t="n">
-        <v>62</v>
+        <v>21</v>
       </c>
     </row>
     <row r="128">
@@ -6704,7 +6706,7 @@
       </c>
       <c r="B128" s="24" t="inlineStr">
         <is>
-          <t>US-OR-CRO-CRR-8S-F</t>
+          <t>US-OR-CRO-CRR-4S-L</t>
         </is>
       </c>
       <c r="C128" s="24" t="inlineStr">
@@ -6728,7 +6730,7 @@
         </is>
       </c>
       <c r="G128" s="23" t="n">
-        <v>53</v>
+        <v>18</v>
       </c>
     </row>
     <row r="129">
@@ -6739,7 +6741,7 @@
       </c>
       <c r="B129" s="24" t="inlineStr">
         <is>
-          <t>US-OR-CRO-CRR-8S-O</t>
+          <t>US-OR-CRO-CRR-4SB-I</t>
         </is>
       </c>
       <c r="C129" s="24" t="inlineStr">
@@ -6759,11 +6761,11 @@
       </c>
       <c r="F129" s="23" t="inlineStr">
         <is>
-          <t>83%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G129" s="23" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="130">
@@ -6774,7 +6776,7 @@
       </c>
       <c r="B130" s="24" t="inlineStr">
         <is>
-          <t>US-OR-CRO-CRR-4S-L</t>
+          <t>US-OR-CRO-CRR-4S-K</t>
         </is>
       </c>
       <c r="C130" s="24" t="inlineStr">
@@ -6798,7 +6800,7 @@
         </is>
       </c>
       <c r="G130" s="23" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="131">
@@ -6809,7 +6811,7 @@
       </c>
       <c r="B131" s="24" t="inlineStr">
         <is>
-          <t>US-OR-CRO-CRR-4SB-I</t>
+          <t>US-OR-CRO-CRR-4SC-B</t>
         </is>
       </c>
       <c r="C131" s="24" t="inlineStr">
@@ -6833,7 +6835,7 @@
         </is>
       </c>
       <c r="G131" s="23" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="132">
@@ -6844,7 +6846,7 @@
       </c>
       <c r="B132" s="24" t="inlineStr">
         <is>
-          <t>US-OR-CRO-CRR-4S-K</t>
+          <t>US-OR-CRO-CRR-8SG-B</t>
         </is>
       </c>
       <c r="C132" s="24" t="inlineStr">
@@ -6868,7 +6870,7 @@
         </is>
       </c>
       <c r="G132" s="23" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="133">
@@ -6879,7 +6881,7 @@
       </c>
       <c r="B133" s="24" t="inlineStr">
         <is>
-          <t>US-OR-CRO-CRR-4SC-B</t>
+          <t>US-OR-CRO-CRR-4SB-C</t>
         </is>
       </c>
       <c r="C133" s="24" t="inlineStr">
@@ -6903,7 +6905,7 @@
         </is>
       </c>
       <c r="G133" s="23" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="134">
@@ -6914,7 +6916,7 @@
       </c>
       <c r="B134" s="24" t="inlineStr">
         <is>
-          <t>US-OR-CRO-CRR-8SG-B</t>
+          <t>US-OR-CRO-CRR-4S-F</t>
         </is>
       </c>
       <c r="C134" s="24" t="inlineStr">
@@ -6938,7 +6940,7 @@
         </is>
       </c>
       <c r="G134" s="23" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="135">
@@ -6949,7 +6951,7 @@
       </c>
       <c r="B135" s="24" t="inlineStr">
         <is>
-          <t>US-OR-CRO-CRR-4SB-C</t>
+          <t>US-OR-CRO-CRR-4SB-J</t>
         </is>
       </c>
       <c r="C135" s="24" t="inlineStr">
@@ -6969,11 +6971,11 @@
       </c>
       <c r="F135" s="23" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>99%</t>
         </is>
       </c>
       <c r="G135" s="23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="136">
@@ -6984,7 +6986,7 @@
       </c>
       <c r="B136" s="24" t="inlineStr">
         <is>
-          <t>US-OR-CRO-CRR-4S-F</t>
+          <t>US-OR-CRO-CRR-4S-N</t>
         </is>
       </c>
       <c r="C136" s="24" t="inlineStr">
@@ -7008,7 +7010,7 @@
         </is>
       </c>
       <c r="G136" s="23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="137">
@@ -7019,7 +7021,7 @@
       </c>
       <c r="B137" s="24" t="inlineStr">
         <is>
-          <t>US-OR-CRO-CRR-4S-N</t>
+          <t>US-OR-CRO-CRR-4SB-D</t>
         </is>
       </c>
       <c r="C137" s="24" t="inlineStr">
@@ -7054,7 +7056,7 @@
       </c>
       <c r="B138" s="24" t="inlineStr">
         <is>
-          <t>US-OR-CRO-CRR-4SB-D</t>
+          <t>US-OR-CRO-CRR-4SB-E</t>
         </is>
       </c>
       <c r="C138" s="24" t="inlineStr">
@@ -7078,7 +7080,7 @@
         </is>
       </c>
       <c r="G138" s="23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="139">
@@ -7089,7 +7091,7 @@
       </c>
       <c r="B139" s="24" t="inlineStr">
         <is>
-          <t>US-OR-CRO-CRR-4SB-E</t>
+          <t>US-OR-CRO-CRR-8S-N</t>
         </is>
       </c>
       <c r="C139" s="24" t="inlineStr">
@@ -7124,7 +7126,7 @@
       </c>
       <c r="B140" s="24" t="inlineStr">
         <is>
-          <t>US-OR-CRO-CRR-8S-N</t>
+          <t>US-OR-CRO-CRR-8SG-A</t>
         </is>
       </c>
       <c r="C140" s="24" t="inlineStr">
@@ -7148,7 +7150,7 @@
         </is>
       </c>
       <c r="G140" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="141">
@@ -7159,7 +7161,7 @@
       </c>
       <c r="B141" s="24" t="inlineStr">
         <is>
-          <t>US-OR-CRO-CRR-8SG-A</t>
+          <t>US-OR-CRO-CRR-8S-E</t>
         </is>
       </c>
       <c r="C141" s="24" t="inlineStr">
@@ -7194,7 +7196,7 @@
       </c>
       <c r="B142" s="24" t="inlineStr">
         <is>
-          <t>US-OR-CRO-CRR-8S-E</t>
+          <t>US-OR-CRO-CRR-8S-Q</t>
         </is>
       </c>
       <c r="C142" s="24" t="inlineStr">
@@ -7214,7 +7216,7 @@
       </c>
       <c r="F142" s="23" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>61%</t>
         </is>
       </c>
       <c r="G142" s="23" t="n">
@@ -7229,7 +7231,7 @@
       </c>
       <c r="B143" s="24" t="inlineStr">
         <is>
-          <t>US-OR-CRO-CRR-8S-Q</t>
+          <t>US-OR-CRO-CRR-1S-Q</t>
         </is>
       </c>
       <c r="C143" s="24" t="inlineStr">
@@ -7249,7 +7251,7 @@
       </c>
       <c r="F143" s="23" t="inlineStr">
         <is>
-          <t>61%</t>
+          <t>13%</t>
         </is>
       </c>
       <c r="G143" s="23" t="n">
@@ -7719,7 +7721,7 @@
       </c>
       <c r="B157" s="22" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1381-A</t>
+          <t>US-OR-KLA-KLA-1168</t>
         </is>
       </c>
       <c r="C157" s="22" t="inlineStr">
@@ -7739,11 +7741,11 @@
       </c>
       <c r="F157" s="21" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G157" s="21" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="158">
@@ -7754,7 +7756,7 @@
       </c>
       <c r="B158" s="22" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1168</t>
+          <t>US-OR-KLA-KLA-1164</t>
         </is>
       </c>
       <c r="C158" s="22" t="inlineStr">
@@ -7778,7 +7780,7 @@
         </is>
       </c>
       <c r="G158" s="21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="159">
@@ -7789,7 +7791,7 @@
       </c>
       <c r="B159" s="22" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1164</t>
+          <t>US-OR-KLA-KLA-1162</t>
         </is>
       </c>
       <c r="C159" s="22" t="inlineStr">
@@ -7809,7 +7811,7 @@
       </c>
       <c r="F159" s="21" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>99%</t>
         </is>
       </c>
       <c r="G159" s="21" t="n">
@@ -7824,7 +7826,7 @@
       </c>
       <c r="B160" s="22" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1162</t>
+          <t>US-OR-KLA-KLA-1167</t>
         </is>
       </c>
       <c r="C160" s="22" t="inlineStr">
@@ -7844,11 +7846,11 @@
       </c>
       <c r="F160" s="21" t="inlineStr">
         <is>
-          <t>99%</t>
+          <t>59%</t>
         </is>
       </c>
       <c r="G160" s="21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="161">
@@ -7859,7 +7861,7 @@
       </c>
       <c r="B161" s="22" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1167</t>
+          <t>US-OR-KLA-KLA-1381-B</t>
         </is>
       </c>
       <c r="C161" s="22" t="inlineStr">
@@ -7879,7 +7881,7 @@
       </c>
       <c r="F161" s="21" t="inlineStr">
         <is>
-          <t>59%</t>
+          <t>16%</t>
         </is>
       </c>
       <c r="G161" s="21" t="n">
@@ -7887,38 +7889,38 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="21" t="inlineStr">
+      <c r="A162" s="23" t="inlineStr">
         <is>
           <t>97624</t>
         </is>
       </c>
-      <c r="B162" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-KLA-1381-B</t>
-        </is>
-      </c>
-      <c r="C162" s="22" t="inlineStr">
+      <c r="B162" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-KLA-KLA-1176</t>
+        </is>
+      </c>
+      <c r="C162" s="24" t="inlineStr">
         <is>
           <t>Wrights Spring</t>
         </is>
       </c>
-      <c r="D162" s="22" t="inlineStr">
+      <c r="D162" s="24" t="inlineStr">
         <is>
           <t>Klamath</t>
         </is>
       </c>
-      <c r="E162" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F162" s="21" t="inlineStr">
-        <is>
-          <t>16%</t>
-        </is>
-      </c>
-      <c r="G162" s="21" t="n">
-        <v>1</v>
+      <c r="E162" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F162" s="23" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G162" s="23" t="n">
+        <v>56</v>
       </c>
     </row>
     <row r="163">
@@ -7929,7 +7931,7 @@
       </c>
       <c r="B163" s="24" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1176</t>
+          <t>US-OR-KLA-KLA-1416</t>
         </is>
       </c>
       <c r="C163" s="24" t="inlineStr">
@@ -7953,7 +7955,7 @@
         </is>
       </c>
       <c r="G163" s="23" t="n">
-        <v>56</v>
+        <v>47</v>
       </c>
     </row>
     <row r="164">
@@ -7964,7 +7966,7 @@
       </c>
       <c r="B164" s="24" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1416</t>
+          <t>US-OR-KLA-KLA-1171</t>
         </is>
       </c>
       <c r="C164" s="24" t="inlineStr">
@@ -7988,7 +7990,7 @@
         </is>
       </c>
       <c r="G164" s="23" t="n">
-        <v>47</v>
+        <v>19</v>
       </c>
     </row>
     <row r="165">
@@ -7999,7 +8001,7 @@
       </c>
       <c r="B165" s="24" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1171</t>
+          <t>US-OR-KLA-KLA-1156</t>
         </is>
       </c>
       <c r="C165" s="24" t="inlineStr">
@@ -8019,11 +8021,11 @@
       </c>
       <c r="F165" s="23" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>43%</t>
         </is>
       </c>
       <c r="G165" s="23" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="166">
@@ -8034,7 +8036,7 @@
       </c>
       <c r="B166" s="24" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1156</t>
+          <t>US-OR-KLA-KLA-1401</t>
         </is>
       </c>
       <c r="C166" s="24" t="inlineStr">
@@ -8054,11 +8056,11 @@
       </c>
       <c r="F166" s="23" t="inlineStr">
         <is>
-          <t>43%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G166" s="23" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="167">
@@ -8069,7 +8071,7 @@
       </c>
       <c r="B167" s="24" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1401</t>
+          <t>US-OR-KLA-KLA-1391</t>
         </is>
       </c>
       <c r="C167" s="24" t="inlineStr">
@@ -8093,7 +8095,7 @@
         </is>
       </c>
       <c r="G167" s="23" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="168">
@@ -8104,7 +8106,7 @@
       </c>
       <c r="B168" s="24" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1391</t>
+          <t>US-OR-KLA-FHZ-1583</t>
         </is>
       </c>
       <c r="C168" s="24" t="inlineStr">
@@ -8124,11 +8126,11 @@
       </c>
       <c r="F168" s="23" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="G168" s="23" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="169">
@@ -8139,7 +8141,7 @@
       </c>
       <c r="B169" s="24" t="inlineStr">
         <is>
-          <t>US-OR-KLA-FHZ-1583</t>
+          <t>US-OR-KLA-KLA-1381-A</t>
         </is>
       </c>
       <c r="C169" s="24" t="inlineStr">
@@ -8159,7 +8161,7 @@
       </c>
       <c r="F169" s="23" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="G169" s="23" t="n">
@@ -8209,7 +8211,7 @@
       </c>
       <c r="B171" s="24" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1421</t>
+          <t>US-OR-KLA-KLA-1386</t>
         </is>
       </c>
       <c r="C171" s="24" t="inlineStr">
@@ -8229,81 +8231,81 @@
       </c>
       <c r="F171" s="23" t="inlineStr">
         <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="G171" s="23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="25" t="inlineStr">
+        <is>
+          <t>97624</t>
+        </is>
+      </c>
+      <c r="B172" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-KLA-KLA-1181</t>
+        </is>
+      </c>
+      <c r="C172" s="26" t="inlineStr">
+        <is>
+          <t>Wrights Spring</t>
+        </is>
+      </c>
+      <c r="D172" s="26" t="inlineStr">
+        <is>
+          <t>Klamath</t>
+        </is>
+      </c>
+      <c r="E172" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F172" s="25" t="inlineStr">
+        <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="G171" s="23" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" s="23" t="inlineStr">
+      <c r="G172" s="25" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="25" t="inlineStr">
         <is>
           <t>97624</t>
         </is>
       </c>
-      <c r="B172" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-KLA-1386</t>
-        </is>
-      </c>
-      <c r="C172" s="24" t="inlineStr">
+      <c r="B173" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-KLA-KLA-1186</t>
+        </is>
+      </c>
+      <c r="C173" s="26" t="inlineStr">
         <is>
           <t>Wrights Spring</t>
         </is>
       </c>
-      <c r="D172" s="24" t="inlineStr">
+      <c r="D173" s="26" t="inlineStr">
         <is>
           <t>Klamath</t>
         </is>
       </c>
-      <c r="E172" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F172" s="23" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G172" s="23" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" s="23" t="inlineStr">
-        <is>
-          <t>97624</t>
-        </is>
-      </c>
-      <c r="B173" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-FHZ-1584-B</t>
-        </is>
-      </c>
-      <c r="C173" s="24" t="inlineStr">
-        <is>
-          <t>Wrights Spring</t>
-        </is>
-      </c>
-      <c r="D173" s="24" t="inlineStr">
-        <is>
-          <t>Klamath</t>
-        </is>
-      </c>
-      <c r="E173" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F173" s="23" t="inlineStr">
-        <is>
-          <t>1%</t>
-        </is>
-      </c>
-      <c r="G173" s="23" t="n">
-        <v>1</v>
+      <c r="E173" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F173" s="25" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G173" s="25" t="n">
+        <v>39</v>
       </c>
     </row>
     <row r="174">
@@ -8314,7 +8316,7 @@
       </c>
       <c r="B174" s="26" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1181</t>
+          <t>US-OR-KLA-KLA-1452</t>
         </is>
       </c>
       <c r="C174" s="26" t="inlineStr">
@@ -8334,11 +8336,11 @@
       </c>
       <c r="F174" s="25" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>95%</t>
         </is>
       </c>
       <c r="G174" s="25" t="n">
-        <v>71</v>
+        <v>32</v>
       </c>
     </row>
     <row r="175">
@@ -8349,7 +8351,7 @@
       </c>
       <c r="B175" s="26" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1186</t>
+          <t>US-OR-KLA-KLA-1446</t>
         </is>
       </c>
       <c r="C175" s="26" t="inlineStr">
@@ -8373,7 +8375,7 @@
         </is>
       </c>
       <c r="G175" s="25" t="n">
-        <v>39</v>
+        <v>15</v>
       </c>
     </row>
     <row r="176">
@@ -8384,7 +8386,7 @@
       </c>
       <c r="B176" s="26" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1452</t>
+          <t>US-OR-KLA-KLA-1031</t>
         </is>
       </c>
       <c r="C176" s="26" t="inlineStr">
@@ -8404,11 +8406,11 @@
       </c>
       <c r="F176" s="25" t="inlineStr">
         <is>
-          <t>95%</t>
+          <t>70%</t>
         </is>
       </c>
       <c r="G176" s="25" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
     </row>
     <row r="177">
@@ -8419,7 +8421,7 @@
       </c>
       <c r="B177" s="26" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1446</t>
+          <t>US-OR-KLA-KLA-1191</t>
         </is>
       </c>
       <c r="C177" s="26" t="inlineStr">
@@ -8443,7 +8445,7 @@
         </is>
       </c>
       <c r="G177" s="25" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
     </row>
     <row r="178">
@@ -8454,7 +8456,7 @@
       </c>
       <c r="B178" s="26" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1031</t>
+          <t>US-OR-KLA-KLA-1441</t>
         </is>
       </c>
       <c r="C178" s="26" t="inlineStr">
@@ -8474,11 +8476,11 @@
       </c>
       <c r="F178" s="25" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G178" s="25" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="179">
@@ -8489,7 +8491,7 @@
       </c>
       <c r="B179" s="26" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1191</t>
+          <t>US-OR-KLA-KLA-1201</t>
         </is>
       </c>
       <c r="C179" s="26" t="inlineStr">
@@ -8513,7 +8515,7 @@
         </is>
       </c>
       <c r="G179" s="25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="180">
@@ -8524,7 +8526,7 @@
       </c>
       <c r="B180" s="26" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1441</t>
+          <t>US-OR-KLA-KLA-1421</t>
         </is>
       </c>
       <c r="C180" s="26" t="inlineStr">
@@ -8548,7 +8550,7 @@
         </is>
       </c>
       <c r="G180" s="25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="181">
@@ -8559,7 +8561,7 @@
       </c>
       <c r="B181" s="26" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1201</t>
+          <t>US-OR-KLA-KLA-1361</t>
         </is>
       </c>
       <c r="C181" s="26" t="inlineStr">
@@ -8579,7 +8581,7 @@
       </c>
       <c r="F181" s="25" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>83%</t>
         </is>
       </c>
       <c r="G181" s="25" t="n">
@@ -8594,7 +8596,7 @@
       </c>
       <c r="B182" s="26" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1361</t>
+          <t>US-OR-KLA-FHZ-1584-A</t>
         </is>
       </c>
       <c r="C182" s="26" t="inlineStr">
@@ -8614,11 +8616,11 @@
       </c>
       <c r="F182" s="25" t="inlineStr">
         <is>
-          <t>83%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="G182" s="25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="183">
@@ -8629,7 +8631,7 @@
       </c>
       <c r="B183" s="26" t="inlineStr">
         <is>
-          <t>US-OR-KLA-FHZ-1584-A</t>
+          <t>US-OR-KLA-KLA-1371</t>
         </is>
       </c>
       <c r="C183" s="26" t="inlineStr">
@@ -8649,7 +8651,7 @@
       </c>
       <c r="F183" s="25" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>1%</t>
         </is>
       </c>
       <c r="G183" s="25" t="n">
@@ -8664,7 +8666,7 @@
       </c>
       <c r="B184" s="26" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1371</t>
+          <t>US-OR-KLA-FHZ-1584-B</t>
         </is>
       </c>
       <c r="C184" s="26" t="inlineStr">
@@ -8979,7 +8981,7 @@
       </c>
       <c r="B193" s="22" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1426</t>
+          <t>US-OR-KLA-KLA-1717</t>
         </is>
       </c>
       <c r="C193" s="22" t="inlineStr">
@@ -8999,11 +9001,11 @@
       </c>
       <c r="F193" s="21" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="G193" s="21" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="194">
@@ -9014,7 +9016,7 @@
       </c>
       <c r="B194" s="22" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1381-A</t>
+          <t>US-OR-KLA-KLA-1381-B</t>
         </is>
       </c>
       <c r="C194" s="22" t="inlineStr">
@@ -9034,11 +9036,11 @@
       </c>
       <c r="F194" s="21" t="inlineStr">
         <is>
-          <t>54%</t>
+          <t>47%</t>
         </is>
       </c>
       <c r="G194" s="21" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="195">
@@ -9049,7 +9051,7 @@
       </c>
       <c r="B195" s="22" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1566</t>
+          <t>US-OR-KLA-FHZ-1582</t>
         </is>
       </c>
       <c r="C195" s="22" t="inlineStr">
@@ -9069,11 +9071,11 @@
       </c>
       <c r="F195" s="21" t="inlineStr">
         <is>
-          <t>54%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G195" s="21" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="196">
@@ -9084,7 +9086,7 @@
       </c>
       <c r="B196" s="22" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1717</t>
+          <t>US-OR-KLA-KLA-1167</t>
         </is>
       </c>
       <c r="C196" s="22" t="inlineStr">
@@ -9104,221 +9106,221 @@
       </c>
       <c r="F196" s="21" t="inlineStr">
         <is>
-          <t>7%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G196" s="21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="23" t="inlineStr">
+        <is>
+          <t>97639</t>
+        </is>
+      </c>
+      <c r="B197" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-KLA-KLA-1386</t>
+        </is>
+      </c>
+      <c r="C197" s="24" t="inlineStr">
+        <is>
+          <t>Wrights Spring</t>
+        </is>
+      </c>
+      <c r="D197" s="24" t="inlineStr">
+        <is>
+          <t>Klamath</t>
+        </is>
+      </c>
+      <c r="E197" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F197" s="23" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G197" s="23" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="23" t="inlineStr">
+        <is>
+          <t>97639</t>
+        </is>
+      </c>
+      <c r="B198" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-KLA-KLA-1426</t>
+        </is>
+      </c>
+      <c r="C198" s="24" t="inlineStr">
+        <is>
+          <t>Wrights Spring</t>
+        </is>
+      </c>
+      <c r="D198" s="24" t="inlineStr">
+        <is>
+          <t>Klamath</t>
+        </is>
+      </c>
+      <c r="E198" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F198" s="23" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G198" s="23" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="23" t="inlineStr">
+        <is>
+          <t>97639</t>
+        </is>
+      </c>
+      <c r="B199" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-KLA-FHZ-1583</t>
+        </is>
+      </c>
+      <c r="C199" s="24" t="inlineStr">
+        <is>
+          <t>Wrights Spring</t>
+        </is>
+      </c>
+      <c r="D199" s="24" t="inlineStr">
+        <is>
+          <t>Klamath</t>
+        </is>
+      </c>
+      <c r="E199" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F199" s="23" t="inlineStr">
+        <is>
+          <t>71%</t>
+        </is>
+      </c>
+      <c r="G199" s="23" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="23" t="inlineStr">
+        <is>
+          <t>97639</t>
+        </is>
+      </c>
+      <c r="B200" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-KLA-KLA-1566</t>
+        </is>
+      </c>
+      <c r="C200" s="24" t="inlineStr">
+        <is>
+          <t>Wrights Spring</t>
+        </is>
+      </c>
+      <c r="D200" s="24" t="inlineStr">
+        <is>
+          <t>Klamath</t>
+        </is>
+      </c>
+      <c r="E200" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F200" s="23" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="G200" s="23" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="23" t="inlineStr">
+        <is>
+          <t>97639</t>
+        </is>
+      </c>
+      <c r="B201" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-KLA-KLA-1381-A</t>
+        </is>
+      </c>
+      <c r="C201" s="24" t="inlineStr">
+        <is>
+          <t>Wrights Spring</t>
+        </is>
+      </c>
+      <c r="D201" s="24" t="inlineStr">
+        <is>
+          <t>Klamath</t>
+        </is>
+      </c>
+      <c r="E201" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F201" s="23" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="G201" s="23" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="23" t="inlineStr">
+        <is>
+          <t>97639</t>
+        </is>
+      </c>
+      <c r="B202" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-KLA-KLA-1431</t>
+        </is>
+      </c>
+      <c r="C202" s="24" t="inlineStr">
+        <is>
+          <t>Wrights Spring</t>
+        </is>
+      </c>
+      <c r="D202" s="24" t="inlineStr">
+        <is>
+          <t>Klamath</t>
+        </is>
+      </c>
+      <c r="E202" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F202" s="23" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G202" s="23" t="n">
         <v>2</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" s="21" t="inlineStr">
-        <is>
-          <t>97639</t>
-        </is>
-      </c>
-      <c r="B197" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-KLA-1718-A</t>
-        </is>
-      </c>
-      <c r="C197" s="22" t="inlineStr">
-        <is>
-          <t>Wrights Spring</t>
-        </is>
-      </c>
-      <c r="D197" s="22" t="inlineStr">
-        <is>
-          <t>Klamath</t>
-        </is>
-      </c>
-      <c r="E197" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F197" s="21" t="inlineStr">
-        <is>
-          <t>38%</t>
-        </is>
-      </c>
-      <c r="G197" s="21" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" s="21" t="inlineStr">
-        <is>
-          <t>97639</t>
-        </is>
-      </c>
-      <c r="B198" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-KLA-1572</t>
-        </is>
-      </c>
-      <c r="C198" s="22" t="inlineStr">
-        <is>
-          <t>Wrights Spring</t>
-        </is>
-      </c>
-      <c r="D198" s="22" t="inlineStr">
-        <is>
-          <t>Klamath</t>
-        </is>
-      </c>
-      <c r="E198" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F198" s="21" t="inlineStr">
-        <is>
-          <t>18%</t>
-        </is>
-      </c>
-      <c r="G198" s="21" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" s="21" t="inlineStr">
-        <is>
-          <t>97639</t>
-        </is>
-      </c>
-      <c r="B199" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-KLA-1381-B</t>
-        </is>
-      </c>
-      <c r="C199" s="22" t="inlineStr">
-        <is>
-          <t>Wrights Spring</t>
-        </is>
-      </c>
-      <c r="D199" s="22" t="inlineStr">
-        <is>
-          <t>Klamath</t>
-        </is>
-      </c>
-      <c r="E199" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F199" s="21" t="inlineStr">
-        <is>
-          <t>47%</t>
-        </is>
-      </c>
-      <c r="G199" s="21" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" s="21" t="inlineStr">
-        <is>
-          <t>97639</t>
-        </is>
-      </c>
-      <c r="B200" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-KLA-1718-B</t>
-        </is>
-      </c>
-      <c r="C200" s="22" t="inlineStr">
-        <is>
-          <t>Wrights Spring</t>
-        </is>
-      </c>
-      <c r="D200" s="22" t="inlineStr">
-        <is>
-          <t>Klamath</t>
-        </is>
-      </c>
-      <c r="E200" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F200" s="21" t="inlineStr">
-        <is>
-          <t>2%</t>
-        </is>
-      </c>
-      <c r="G200" s="21" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" s="21" t="inlineStr">
-        <is>
-          <t>97639</t>
-        </is>
-      </c>
-      <c r="B201" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-FHZ-1582</t>
-        </is>
-      </c>
-      <c r="C201" s="22" t="inlineStr">
-        <is>
-          <t>Wrights Spring</t>
-        </is>
-      </c>
-      <c r="D201" s="22" t="inlineStr">
-        <is>
-          <t>Klamath</t>
-        </is>
-      </c>
-      <c r="E201" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F201" s="21" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G201" s="21" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" s="21" t="inlineStr">
-        <is>
-          <t>97639</t>
-        </is>
-      </c>
-      <c r="B202" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-KLA-1167</t>
-        </is>
-      </c>
-      <c r="C202" s="22" t="inlineStr">
-        <is>
-          <t>Wrights Spring</t>
-        </is>
-      </c>
-      <c r="D202" s="22" t="inlineStr">
-        <is>
-          <t>Klamath</t>
-        </is>
-      </c>
-      <c r="E202" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F202" s="21" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G202" s="21" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="203">
@@ -9329,7 +9331,7 @@
       </c>
       <c r="B203" s="24" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1386</t>
+          <t>US-OR-KLA-KLA-1718-A</t>
         </is>
       </c>
       <c r="C203" s="24" t="inlineStr">
@@ -9349,11 +9351,11 @@
       </c>
       <c r="F203" s="23" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>38%</t>
         </is>
       </c>
       <c r="G203" s="23" t="n">
-        <v>63</v>
+        <v>1</v>
       </c>
     </row>
     <row r="204">
@@ -9364,7 +9366,7 @@
       </c>
       <c r="B204" s="24" t="inlineStr">
         <is>
-          <t>US-OR-KLA-FHZ-1583</t>
+          <t>US-OR-KLA-KLA-1572</t>
         </is>
       </c>
       <c r="C204" s="24" t="inlineStr">
@@ -9384,11 +9386,11 @@
       </c>
       <c r="F204" s="23" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="G204" s="23" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="205">
@@ -9399,100 +9401,100 @@
       </c>
       <c r="B205" s="24" t="inlineStr">
         <is>
+          <t>US-OR-KLA-KLA-1718-B</t>
+        </is>
+      </c>
+      <c r="C205" s="24" t="inlineStr">
+        <is>
+          <t>Wrights Spring</t>
+        </is>
+      </c>
+      <c r="D205" s="24" t="inlineStr">
+        <is>
+          <t>Klamath</t>
+        </is>
+      </c>
+      <c r="E205" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F205" s="23" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="G205" s="23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="25" t="inlineStr">
+        <is>
+          <t>97639</t>
+        </is>
+      </c>
+      <c r="B206" s="26" t="inlineStr">
+        <is>
           <t>US-OR-KLA-KLA-1577</t>
         </is>
       </c>
-      <c r="C205" s="24" t="inlineStr">
+      <c r="C206" s="26" t="inlineStr">
         <is>
           <t>Wrights Spring</t>
         </is>
       </c>
-      <c r="D205" s="24" t="inlineStr">
+      <c r="D206" s="26" t="inlineStr">
         <is>
           <t>Klamath</t>
         </is>
       </c>
-      <c r="E205" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F205" s="23" t="inlineStr">
+      <c r="E206" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F206" s="25" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="G205" s="23" t="n">
+      <c r="G206" s="25" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="206">
-      <c r="A206" s="23" t="inlineStr">
+    <row r="207">
+      <c r="A207" s="25" t="inlineStr">
         <is>
           <t>97639</t>
         </is>
       </c>
-      <c r="B206" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-KLA-1431</t>
-        </is>
-      </c>
-      <c r="C206" s="24" t="inlineStr">
+      <c r="B207" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-KLA-KLA-1371</t>
+        </is>
+      </c>
+      <c r="C207" s="26" t="inlineStr">
         <is>
           <t>Wrights Spring</t>
         </is>
       </c>
-      <c r="D206" s="24" t="inlineStr">
+      <c r="D207" s="26" t="inlineStr">
         <is>
           <t>Klamath</t>
         </is>
       </c>
-      <c r="E206" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F206" s="23" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G206" s="23" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" s="23" t="inlineStr">
-        <is>
-          <t>97639</t>
-        </is>
-      </c>
-      <c r="B207" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-FHZ-1584-B</t>
-        </is>
-      </c>
-      <c r="C207" s="24" t="inlineStr">
-        <is>
-          <t>Wrights Spring</t>
-        </is>
-      </c>
-      <c r="D207" s="24" t="inlineStr">
-        <is>
-          <t>Klamath</t>
-        </is>
-      </c>
-      <c r="E207" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F207" s="23" t="inlineStr">
-        <is>
-          <t>99%</t>
-        </is>
-      </c>
-      <c r="G207" s="23" t="n">
+      <c r="E207" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F207" s="25" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="G207" s="25" t="n">
         <v>2</v>
       </c>
     </row>
@@ -9504,7 +9506,7 @@
       </c>
       <c r="B208" s="26" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1371</t>
+          <t>US-OR-KLA-FHZ-1584-B</t>
         </is>
       </c>
       <c r="C208" s="26" t="inlineStr">
@@ -9524,7 +9526,7 @@
       </c>
       <c r="F208" s="25" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>99%</t>
         </is>
       </c>
       <c r="G208" s="25" t="n">
@@ -10444,12 +10446,12 @@
     <row r="235">
       <c r="A235" s="21" t="inlineStr">
         <is>
-          <t>97621</t>
+          <t>97625</t>
         </is>
       </c>
       <c r="B235" s="22" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1572</t>
+          <t>US-OR-KLA-KLA-1713-B</t>
         </is>
       </c>
       <c r="C235" s="22" t="inlineStr">
@@ -10469,22 +10471,22 @@
       </c>
       <c r="F235" s="21" t="inlineStr">
         <is>
-          <t>31%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="G235" s="21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="21" t="inlineStr">
         <is>
-          <t>97621</t>
+          <t>97625</t>
         </is>
       </c>
       <c r="B236" s="22" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1566</t>
+          <t>US-OR-KLA-KLA-1713-A</t>
         </is>
       </c>
       <c r="C236" s="22" t="inlineStr">
@@ -10504,7 +10506,7 @@
       </c>
       <c r="F236" s="21" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G236" s="21" t="n">
@@ -10514,12 +10516,12 @@
     <row r="237">
       <c r="A237" s="23" t="inlineStr">
         <is>
-          <t>97621</t>
+          <t>97625</t>
         </is>
       </c>
       <c r="B237" s="24" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1472</t>
+          <t>US-OR-KLA-KLA-1707</t>
         </is>
       </c>
       <c r="C237" s="24" t="inlineStr">
@@ -10539,22 +10541,22 @@
       </c>
       <c r="F237" s="23" t="inlineStr">
         <is>
-          <t>93%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="G237" s="23" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="23" t="inlineStr">
         <is>
-          <t>97621</t>
+          <t>97625</t>
         </is>
       </c>
       <c r="B238" s="24" t="inlineStr">
         <is>
-          <t>US-OR-KLA-FHZ-1584-B</t>
+          <t>US-OR-KLA-KLA-1941</t>
         </is>
       </c>
       <c r="C238" s="24" t="inlineStr">
@@ -10574,57 +10576,57 @@
       </c>
       <c r="F238" s="23" t="inlineStr">
         <is>
+          <t>23%</t>
+        </is>
+      </c>
+      <c r="G238" s="23" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="23" t="inlineStr">
+        <is>
+          <t>97625</t>
+        </is>
+      </c>
+      <c r="B239" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-KLA-KLA-1956</t>
+        </is>
+      </c>
+      <c r="C239" s="24" t="inlineStr">
+        <is>
+          <t>Wrights Spring</t>
+        </is>
+      </c>
+      <c r="D239" s="24" t="inlineStr">
+        <is>
+          <t>Klamath</t>
+        </is>
+      </c>
+      <c r="E239" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F239" s="23" t="inlineStr">
+        <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="G238" s="23" t="n">
+      <c r="G239" s="23" t="n">
         <v>1</v>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" s="25" t="inlineStr">
-        <is>
-          <t>97621</t>
-        </is>
-      </c>
-      <c r="B239" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-KLA-1471</t>
-        </is>
-      </c>
-      <c r="C239" s="26" t="inlineStr">
-        <is>
-          <t>Wrights Spring</t>
-        </is>
-      </c>
-      <c r="D239" s="26" t="inlineStr">
-        <is>
-          <t>Klamath</t>
-        </is>
-      </c>
-      <c r="E239" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F239" s="25" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G239" s="25" t="n">
-        <v>18</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="25" t="inlineStr">
         <is>
-          <t>97621</t>
+          <t>97625</t>
         </is>
       </c>
       <c r="B240" s="26" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1586</t>
+          <t>US-OR-KLA-KLA-2261</t>
         </is>
       </c>
       <c r="C240" s="26" t="inlineStr">
@@ -10644,22 +10646,22 @@
       </c>
       <c r="F240" s="25" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>31%</t>
         </is>
       </c>
       <c r="G240" s="25" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="25" t="inlineStr">
         <is>
-          <t>97621</t>
+          <t>97625</t>
         </is>
       </c>
       <c r="B241" s="26" t="inlineStr">
         <is>
-          <t>US-OR-KLA-FHZ-1584-A</t>
+          <t>US-OR-KLA-KLA-1946</t>
         </is>
       </c>
       <c r="C241" s="26" t="inlineStr">
@@ -10679,22 +10681,22 @@
       </c>
       <c r="F241" s="25" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="G241" s="25" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="25" t="inlineStr">
         <is>
-          <t>97621</t>
+          <t>97625</t>
         </is>
       </c>
       <c r="B242" s="26" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1452</t>
+          <t>US-OR-KLA-KLA-1701</t>
         </is>
       </c>
       <c r="C242" s="26" t="inlineStr">
@@ -10714,22 +10716,22 @@
       </c>
       <c r="F242" s="25" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G242" s="25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="25" t="inlineStr">
         <is>
-          <t>97621</t>
+          <t>97625</t>
         </is>
       </c>
       <c r="B243" s="26" t="inlineStr">
         <is>
-          <t>US-OR-KLA-FHZ-1585</t>
+          <t>US-OR-KLA-KLA-1361</t>
         </is>
       </c>
       <c r="C243" s="26" t="inlineStr">
@@ -10749,7 +10751,7 @@
       </c>
       <c r="F243" s="25" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G243" s="25" t="n">
@@ -10759,22 +10761,22 @@
     <row r="244">
       <c r="A244" s="21" t="inlineStr">
         <is>
-          <t>97625</t>
+          <t>97827</t>
         </is>
       </c>
       <c r="B244" s="22" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1713-B</t>
+          <t>US-OR-UNI-UCO-140618N</t>
         </is>
       </c>
       <c r="C244" s="22" t="inlineStr">
         <is>
-          <t>Wrights Spring</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D244" s="22" t="inlineStr">
         <is>
-          <t>Klamath</t>
+          <t>Umatilla, Union</t>
         </is>
       </c>
       <c r="E244" s="21" t="inlineStr">
@@ -10784,32 +10786,32 @@
       </c>
       <c r="F244" s="21" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>68%</t>
         </is>
       </c>
       <c r="G244" s="21" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="21" t="inlineStr">
         <is>
-          <t>97625</t>
+          <t>97827</t>
         </is>
       </c>
       <c r="B245" s="22" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1713-A</t>
+          <t>US-OR-UNI-UCO-140624N-B</t>
         </is>
       </c>
       <c r="C245" s="22" t="inlineStr">
         <is>
-          <t>Wrights Spring</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D245" s="22" t="inlineStr">
         <is>
-          <t>Klamath</t>
+          <t>Umatilla, Union</t>
         </is>
       </c>
       <c r="E245" s="21" t="inlineStr">
@@ -10819,137 +10821,137 @@
       </c>
       <c r="F245" s="21" t="inlineStr">
         <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="G245" s="21" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="21" t="inlineStr">
+        <is>
+          <t>97827</t>
+        </is>
+      </c>
+      <c r="B246" s="22" t="inlineStr">
+        <is>
+          <t>US-OR-UNI-UCO-140624S</t>
+        </is>
+      </c>
+      <c r="C246" s="22" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D246" s="22" t="inlineStr">
+        <is>
+          <t>Umatilla, Union</t>
+        </is>
+      </c>
+      <c r="E246" s="21" t="inlineStr">
+        <is>
+          <t>Level 3 — GO NOW</t>
+        </is>
+      </c>
+      <c r="F246" s="21" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="G246" s="21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="21" t="inlineStr">
+        <is>
+          <t>97827</t>
+        </is>
+      </c>
+      <c r="B247" s="22" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-1406030-A</t>
+        </is>
+      </c>
+      <c r="C247" s="22" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D247" s="22" t="inlineStr">
+        <is>
+          <t>Umatilla, Union</t>
+        </is>
+      </c>
+      <c r="E247" s="21" t="inlineStr">
+        <is>
+          <t>Level 3 — GO NOW</t>
+        </is>
+      </c>
+      <c r="F247" s="21" t="inlineStr">
+        <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="G245" s="21" t="n">
+      <c r="G247" s="21" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="246">
-      <c r="A246" s="23" t="inlineStr">
-        <is>
-          <t>97625</t>
-        </is>
-      </c>
-      <c r="B246" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-KLA-1707</t>
-        </is>
-      </c>
-      <c r="C246" s="24" t="inlineStr">
-        <is>
-          <t>Wrights Spring</t>
-        </is>
-      </c>
-      <c r="D246" s="24" t="inlineStr">
-        <is>
-          <t>Klamath</t>
-        </is>
-      </c>
-      <c r="E246" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F246" s="23" t="inlineStr">
-        <is>
-          <t>84%</t>
-        </is>
-      </c>
-      <c r="G246" s="23" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" s="23" t="inlineStr">
-        <is>
-          <t>97625</t>
-        </is>
-      </c>
-      <c r="B247" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-KLA-1941</t>
-        </is>
-      </c>
-      <c r="C247" s="24" t="inlineStr">
-        <is>
-          <t>Wrights Spring</t>
-        </is>
-      </c>
-      <c r="D247" s="24" t="inlineStr">
-        <is>
-          <t>Klamath</t>
-        </is>
-      </c>
-      <c r="E247" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F247" s="23" t="inlineStr">
-        <is>
-          <t>23%</t>
-        </is>
-      </c>
-      <c r="G247" s="23" t="n">
-        <v>4</v>
-      </c>
-    </row>
     <row r="248">
-      <c r="A248" s="23" t="inlineStr">
-        <is>
-          <t>97625</t>
-        </is>
-      </c>
-      <c r="B248" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-KLA-1956</t>
-        </is>
-      </c>
-      <c r="C248" s="24" t="inlineStr">
-        <is>
-          <t>Wrights Spring</t>
-        </is>
-      </c>
-      <c r="D248" s="24" t="inlineStr">
-        <is>
-          <t>Klamath</t>
-        </is>
-      </c>
-      <c r="E248" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F248" s="23" t="inlineStr">
+      <c r="A248" s="21" t="inlineStr">
+        <is>
+          <t>97827</t>
+        </is>
+      </c>
+      <c r="B248" s="22" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-1406024A</t>
+        </is>
+      </c>
+      <c r="C248" s="22" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D248" s="22" t="inlineStr">
+        <is>
+          <t>Umatilla, Union</t>
+        </is>
+      </c>
+      <c r="E248" s="21" t="inlineStr">
+        <is>
+          <t>Level 3 — GO NOW</t>
+        </is>
+      </c>
+      <c r="F248" s="21" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="G248" s="23" t="n">
+      <c r="G248" s="21" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="25" t="inlineStr">
         <is>
-          <t>97625</t>
+          <t>97827</t>
         </is>
       </c>
       <c r="B249" s="26" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-2261</t>
+          <t>US-OR-UNI-UCO-1497</t>
         </is>
       </c>
       <c r="C249" s="26" t="inlineStr">
         <is>
-          <t>Wrights Spring</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D249" s="26" t="inlineStr">
         <is>
-          <t>Klamath</t>
+          <t>Umatilla, Union</t>
         </is>
       </c>
       <c r="E249" s="25" t="inlineStr">
@@ -10959,32 +10961,32 @@
       </c>
       <c r="F249" s="25" t="inlineStr">
         <is>
-          <t>31%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="G249" s="25" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="25" t="inlineStr">
         <is>
-          <t>97625</t>
+          <t>97827</t>
         </is>
       </c>
       <c r="B250" s="26" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1946</t>
+          <t>US-OR-UNI-UCO-1505</t>
         </is>
       </c>
       <c r="C250" s="26" t="inlineStr">
         <is>
-          <t>Wrights Spring</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D250" s="26" t="inlineStr">
         <is>
-          <t>Klamath</t>
+          <t>Umatilla, Union</t>
         </is>
       </c>
       <c r="E250" s="25" t="inlineStr">
@@ -10994,32 +10996,32 @@
       </c>
       <c r="F250" s="25" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>53%</t>
         </is>
       </c>
       <c r="G250" s="25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="25" t="inlineStr">
         <is>
-          <t>97625</t>
+          <t>97827</t>
         </is>
       </c>
       <c r="B251" s="26" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1701</t>
+          <t>US-OR-UNI-UCO-1513</t>
         </is>
       </c>
       <c r="C251" s="26" t="inlineStr">
         <is>
-          <t>Wrights Spring</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D251" s="26" t="inlineStr">
         <is>
-          <t>Klamath</t>
+          <t>Umatilla, Union</t>
         </is>
       </c>
       <c r="E251" s="25" t="inlineStr">
@@ -11029,7 +11031,7 @@
       </c>
       <c r="F251" s="25" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>1%</t>
         </is>
       </c>
       <c r="G251" s="25" t="n">
@@ -11039,22 +11041,22 @@
     <row r="252">
       <c r="A252" s="25" t="inlineStr">
         <is>
-          <t>97625</t>
+          <t>97827</t>
         </is>
       </c>
       <c r="B252" s="26" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1361</t>
+          <t>US-OR-UNI-UCO-1495</t>
         </is>
       </c>
       <c r="C252" s="26" t="inlineStr">
         <is>
-          <t>Wrights Spring</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D252" s="26" t="inlineStr">
         <is>
-          <t>Klamath</t>
+          <t>Umatilla, Union</t>
         </is>
       </c>
       <c r="E252" s="25" t="inlineStr">
@@ -11074,12 +11076,12 @@
     <row r="253">
       <c r="A253" s="21" t="inlineStr">
         <is>
-          <t>97827</t>
+          <t>97862</t>
         </is>
       </c>
       <c r="B253" s="22" t="inlineStr">
         <is>
-          <t>US-OR-UNI-UCO-140618N</t>
+          <t>US-OR-UMA-UMC-123-B</t>
         </is>
       </c>
       <c r="C253" s="22" t="inlineStr">
@@ -11089,7 +11091,7 @@
       </c>
       <c r="D253" s="22" t="inlineStr">
         <is>
-          <t>Umatilla, Union</t>
+          <t>Umatilla</t>
         </is>
       </c>
       <c r="E253" s="21" t="inlineStr">
@@ -11099,22 +11101,22 @@
       </c>
       <c r="F253" s="21" t="inlineStr">
         <is>
-          <t>68%</t>
+          <t>28%</t>
         </is>
       </c>
       <c r="G253" s="21" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="21" t="inlineStr">
         <is>
-          <t>97827</t>
+          <t>97862</t>
         </is>
       </c>
       <c r="B254" s="22" t="inlineStr">
         <is>
-          <t>US-OR-UNI-UCO-140624N-B</t>
+          <t>US-OR-UMA-UMC-121-B</t>
         </is>
       </c>
       <c r="C254" s="22" t="inlineStr">
@@ -11124,7 +11126,7 @@
       </c>
       <c r="D254" s="22" t="inlineStr">
         <is>
-          <t>Umatilla, Union</t>
+          <t>Umatilla</t>
         </is>
       </c>
       <c r="E254" s="21" t="inlineStr">
@@ -11134,57 +11136,57 @@
       </c>
       <c r="F254" s="21" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G254" s="21" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="21" t="inlineStr">
-        <is>
-          <t>97827</t>
-        </is>
-      </c>
-      <c r="B255" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-UNI-UCO-140624S</t>
-        </is>
-      </c>
-      <c r="C255" s="22" t="inlineStr">
+      <c r="A255" s="23" t="inlineStr">
+        <is>
+          <t>97862</t>
+        </is>
+      </c>
+      <c r="B255" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-1406025-B</t>
+        </is>
+      </c>
+      <c r="C255" s="24" t="inlineStr">
         <is>
           <t>No named fire</t>
         </is>
       </c>
-      <c r="D255" s="22" t="inlineStr">
-        <is>
-          <t>Umatilla, Union</t>
-        </is>
-      </c>
-      <c r="E255" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F255" s="21" t="inlineStr">
-        <is>
-          <t>46%</t>
-        </is>
-      </c>
-      <c r="G255" s="21" t="n">
+      <c r="D255" s="24" t="inlineStr">
+        <is>
+          <t>Umatilla</t>
+        </is>
+      </c>
+      <c r="E255" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F255" s="23" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="G255" s="23" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="21" t="inlineStr">
         <is>
-          <t>97827</t>
+          <t>97023</t>
         </is>
       </c>
       <c r="B256" s="22" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-1406030-A</t>
+          <t>77</t>
         </is>
       </c>
       <c r="C256" s="22" t="inlineStr">
@@ -11194,7 +11196,7 @@
       </c>
       <c r="D256" s="22" t="inlineStr">
         <is>
-          <t>Umatilla, Union</t>
+          <t>Clackamas</t>
         </is>
       </c>
       <c r="E256" s="21" t="inlineStr">
@@ -11204,172 +11206,172 @@
       </c>
       <c r="F256" s="21" t="inlineStr">
         <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G256" s="21" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="25" t="inlineStr">
+        <is>
+          <t>97023</t>
+        </is>
+      </c>
+      <c r="B257" s="26" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="C257" s="26" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D257" s="26" t="inlineStr">
+        <is>
+          <t>Clackamas</t>
+        </is>
+      </c>
+      <c r="E257" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F257" s="25" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G257" s="25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="21" t="inlineStr">
+        <is>
+          <t>97859</t>
+        </is>
+      </c>
+      <c r="B258" s="22" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-1406015-D</t>
+        </is>
+      </c>
+      <c r="C258" s="22" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D258" s="22" t="inlineStr">
+        <is>
+          <t>Umatilla</t>
+        </is>
+      </c>
+      <c r="E258" s="21" t="inlineStr">
+        <is>
+          <t>Level 3 — GO NOW</t>
+        </is>
+      </c>
+      <c r="F258" s="21" t="inlineStr">
+        <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="G256" s="21" t="n">
+      <c r="G258" s="21" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="257">
-      <c r="A257" s="21" t="inlineStr">
-        <is>
-          <t>97827</t>
-        </is>
-      </c>
-      <c r="B257" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-1406024A</t>
-        </is>
-      </c>
-      <c r="C257" s="22" t="inlineStr">
+    <row r="259">
+      <c r="A259" s="23" t="inlineStr">
+        <is>
+          <t>97859</t>
+        </is>
+      </c>
+      <c r="B259" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-1406007-B</t>
+        </is>
+      </c>
+      <c r="C259" s="24" t="inlineStr">
         <is>
           <t>No named fire</t>
         </is>
       </c>
-      <c r="D257" s="22" t="inlineStr">
-        <is>
-          <t>Umatilla, Union</t>
-        </is>
-      </c>
-      <c r="E257" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F257" s="21" t="inlineStr">
+      <c r="D259" s="24" t="inlineStr">
+        <is>
+          <t>Umatilla</t>
+        </is>
+      </c>
+      <c r="E259" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F259" s="23" t="inlineStr">
+        <is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="G259" s="23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="23" t="inlineStr">
+        <is>
+          <t>97028</t>
+        </is>
+      </c>
+      <c r="B260" s="24" t="inlineStr">
+        <is>
+          <t>White River</t>
+        </is>
+      </c>
+      <c r="C260" s="24" t="inlineStr">
+        <is>
+          <t>Grasshopper</t>
+        </is>
+      </c>
+      <c r="D260" s="24" t="inlineStr">
+        <is>
+          <t>Clackamas, Hood River</t>
+        </is>
+      </c>
+      <c r="E260" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F260" s="23" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="G257" s="21" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" s="25" t="inlineStr">
-        <is>
-          <t>97827</t>
-        </is>
-      </c>
-      <c r="B258" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-UNI-UCO-1497</t>
-        </is>
-      </c>
-      <c r="C258" s="26" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D258" s="26" t="inlineStr">
-        <is>
-          <t>Umatilla, Union</t>
-        </is>
-      </c>
-      <c r="E258" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F258" s="25" t="inlineStr">
-        <is>
-          <t>45%</t>
-        </is>
-      </c>
-      <c r="G258" s="25" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" s="25" t="inlineStr">
-        <is>
-          <t>97827</t>
-        </is>
-      </c>
-      <c r="B259" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-UNI-UCO-1505</t>
-        </is>
-      </c>
-      <c r="C259" s="26" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D259" s="26" t="inlineStr">
-        <is>
-          <t>Umatilla, Union</t>
-        </is>
-      </c>
-      <c r="E259" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F259" s="25" t="inlineStr">
-        <is>
-          <t>53%</t>
-        </is>
-      </c>
-      <c r="G259" s="25" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" s="25" t="inlineStr">
-        <is>
-          <t>97827</t>
-        </is>
-      </c>
-      <c r="B260" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-UNI-UCO-1513</t>
-        </is>
-      </c>
-      <c r="C260" s="26" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D260" s="26" t="inlineStr">
-        <is>
-          <t>Umatilla, Union</t>
-        </is>
-      </c>
-      <c r="E260" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F260" s="25" t="inlineStr">
-        <is>
-          <t>1%</t>
-        </is>
-      </c>
-      <c r="G260" s="25" t="n">
+      <c r="G260" s="23" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="25" t="inlineStr">
         <is>
-          <t>97827</t>
+          <t>97028</t>
         </is>
       </c>
       <c r="B261" s="26" t="inlineStr">
         <is>
-          <t>US-OR-UNI-UCO-1495</t>
+          <t>60</t>
         </is>
       </c>
       <c r="C261" s="26" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="D261" s="26" t="inlineStr">
         <is>
-          <t>Umatilla, Union</t>
+          <t>Clackamas, Hood River</t>
         </is>
       </c>
       <c r="E261" s="25" t="inlineStr">
@@ -11379,242 +11381,242 @@
       </c>
       <c r="F261" s="25" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="G261" s="25" t="n">
-        <v>1</v>
+        <v>565</v>
       </c>
     </row>
     <row r="262">
-      <c r="A262" s="21" t="inlineStr">
-        <is>
-          <t>97862</t>
-        </is>
-      </c>
-      <c r="B262" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-123-B</t>
-        </is>
-      </c>
-      <c r="C262" s="22" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D262" s="22" t="inlineStr">
-        <is>
-          <t>Umatilla</t>
-        </is>
-      </c>
-      <c r="E262" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F262" s="21" t="inlineStr">
-        <is>
-          <t>28%</t>
-        </is>
-      </c>
-      <c r="G262" s="21" t="n">
-        <v>23</v>
+      <c r="A262" s="25" t="inlineStr">
+        <is>
+          <t>97028</t>
+        </is>
+      </c>
+      <c r="B262" s="26" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="C262" s="26" t="inlineStr">
+        <is>
+          <t>Grasshopper</t>
+        </is>
+      </c>
+      <c r="D262" s="26" t="inlineStr">
+        <is>
+          <t>Clackamas, Hood River</t>
+        </is>
+      </c>
+      <c r="E262" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F262" s="25" t="inlineStr">
+        <is>
+          <t>36%</t>
+        </is>
+      </c>
+      <c r="G262" s="25" t="n">
+        <v>232</v>
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="21" t="inlineStr">
-        <is>
-          <t>97862</t>
-        </is>
-      </c>
-      <c r="B263" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-121-B</t>
-        </is>
-      </c>
-      <c r="C263" s="22" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D263" s="22" t="inlineStr">
-        <is>
-          <t>Umatilla</t>
-        </is>
-      </c>
-      <c r="E263" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F263" s="21" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G263" s="21" t="n">
-        <v>1</v>
+      <c r="A263" s="25" t="inlineStr">
+        <is>
+          <t>97028</t>
+        </is>
+      </c>
+      <c r="B263" s="26" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="C263" s="26" t="inlineStr">
+        <is>
+          <t>Grasshopper</t>
+        </is>
+      </c>
+      <c r="D263" s="26" t="inlineStr">
+        <is>
+          <t>Clackamas, Hood River</t>
+        </is>
+      </c>
+      <c r="E263" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F263" s="25" t="inlineStr">
+        <is>
+          <t>89%</t>
+        </is>
+      </c>
+      <c r="G263" s="25" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="23" t="inlineStr">
         <is>
-          <t>97862</t>
+          <t>97750</t>
         </is>
       </c>
       <c r="B264" s="24" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-1406025-B</t>
+          <t>US-OR-WHE-WHH-070</t>
         </is>
       </c>
       <c r="C264" s="24" t="inlineStr">
         <is>
+          <t>Rowe Creek Complex</t>
+        </is>
+      </c>
+      <c r="D264" s="24" t="inlineStr">
+        <is>
+          <t>Grant, Wheeler</t>
+        </is>
+      </c>
+      <c r="E264" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F264" s="23" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G264" s="23" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="23" t="inlineStr">
+        <is>
+          <t>97750</t>
+        </is>
+      </c>
+      <c r="B265" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-WHE-WHH-068</t>
+        </is>
+      </c>
+      <c r="C265" s="24" t="inlineStr">
+        <is>
+          <t>Rowe Creek Complex</t>
+        </is>
+      </c>
+      <c r="D265" s="24" t="inlineStr">
+        <is>
+          <t>Grant, Wheeler</t>
+        </is>
+      </c>
+      <c r="E265" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F265" s="23" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G265" s="23" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="23" t="inlineStr">
+        <is>
+          <t>97750</t>
+        </is>
+      </c>
+      <c r="B266" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-WHE-WHH-072-A</t>
+        </is>
+      </c>
+      <c r="C266" s="24" t="inlineStr">
+        <is>
+          <t>Rowe Creek Complex</t>
+        </is>
+      </c>
+      <c r="D266" s="24" t="inlineStr">
+        <is>
+          <t>Grant, Wheeler</t>
+        </is>
+      </c>
+      <c r="E266" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F266" s="23" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G266" s="23" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="23" t="inlineStr">
+        <is>
+          <t>97750</t>
+        </is>
+      </c>
+      <c r="B267" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-WHE-WHH-034-A</t>
+        </is>
+      </c>
+      <c r="C267" s="24" t="inlineStr">
+        <is>
           <t>No named fire</t>
         </is>
       </c>
-      <c r="D264" s="24" t="inlineStr">
-        <is>
-          <t>Umatilla</t>
-        </is>
-      </c>
-      <c r="E264" s="23" t="inlineStr">
+      <c r="D267" s="24" t="inlineStr">
+        <is>
+          <t>Grant, Wheeler</t>
+        </is>
+      </c>
+      <c r="E267" s="23" t="inlineStr">
         <is>
           <t>Level 2 — GET SET</t>
         </is>
       </c>
-      <c r="F264" s="23" t="inlineStr">
-        <is>
-          <t>2%</t>
-        </is>
-      </c>
-      <c r="G264" s="23" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" s="21" t="inlineStr">
-        <is>
-          <t>97023</t>
-        </is>
-      </c>
-      <c r="B265" s="22" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="C265" s="22" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D265" s="22" t="inlineStr">
-        <is>
-          <t>Clackamas</t>
-        </is>
-      </c>
-      <c r="E265" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F265" s="21" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G265" s="21" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" s="25" t="inlineStr">
-        <is>
-          <t>97023</t>
-        </is>
-      </c>
-      <c r="B266" s="26" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="C266" s="26" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D266" s="26" t="inlineStr">
-        <is>
-          <t>Clackamas</t>
-        </is>
-      </c>
-      <c r="E266" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F266" s="25" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G266" s="25" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" s="21" t="inlineStr">
-        <is>
-          <t>97859</t>
-        </is>
-      </c>
-      <c r="B267" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-1406015-D</t>
-        </is>
-      </c>
-      <c r="C267" s="22" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D267" s="22" t="inlineStr">
-        <is>
-          <t>Umatilla</t>
-        </is>
-      </c>
-      <c r="E267" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F267" s="21" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G267" s="21" t="n">
-        <v>1</v>
+      <c r="F267" s="23" t="inlineStr">
+        <is>
+          <t>69%</t>
+        </is>
+      </c>
+      <c r="G267" s="23" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="23" t="inlineStr">
         <is>
-          <t>97859</t>
+          <t>97750</t>
         </is>
       </c>
       <c r="B268" s="24" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-1406007-B</t>
+          <t>US-OR-WHE-WHH-072-C</t>
         </is>
       </c>
       <c r="C268" s="24" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Rowe Creek Complex</t>
         </is>
       </c>
       <c r="D268" s="24" t="inlineStr">
         <is>
-          <t>Umatilla</t>
+          <t>Grant, Wheeler</t>
         </is>
       </c>
       <c r="E268" s="23" t="inlineStr">
@@ -11624,32 +11626,32 @@
       </c>
       <c r="F268" s="23" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="G268" s="23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="23" t="inlineStr">
         <is>
-          <t>97028</t>
+          <t>97750</t>
         </is>
       </c>
       <c r="B269" s="24" t="inlineStr">
         <is>
-          <t>White River</t>
+          <t>US-OR-WHE-WHH-090-A</t>
         </is>
       </c>
       <c r="C269" s="24" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Rowe Creek Complex</t>
         </is>
       </c>
       <c r="D269" s="24" t="inlineStr">
         <is>
-          <t>Clackamas, Hood River</t>
+          <t>Grant, Wheeler</t>
         </is>
       </c>
       <c r="E269" s="23" t="inlineStr">
@@ -11659,7 +11661,7 @@
       </c>
       <c r="F269" s="23" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="G269" s="23" t="n">
@@ -11669,22 +11671,22 @@
     <row r="270">
       <c r="A270" s="25" t="inlineStr">
         <is>
-          <t>97028</t>
+          <t>97750</t>
         </is>
       </c>
       <c r="B270" s="26" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>US-OR-WHE-MIT-076</t>
         </is>
       </c>
       <c r="C270" s="26" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Rowe Creek Complex</t>
         </is>
       </c>
       <c r="D270" s="26" t="inlineStr">
         <is>
-          <t>Clackamas, Hood River</t>
+          <t>Grant, Wheeler</t>
         </is>
       </c>
       <c r="E270" s="25" t="inlineStr">
@@ -11694,32 +11696,32 @@
       </c>
       <c r="F270" s="25" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G270" s="25" t="n">
-        <v>565</v>
+        <v>117</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="25" t="inlineStr">
         <is>
-          <t>97028</t>
+          <t>97750</t>
         </is>
       </c>
       <c r="B271" s="26" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>US-OR-WHE-WHH-062</t>
         </is>
       </c>
       <c r="C271" s="26" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Rowe Creek Complex</t>
         </is>
       </c>
       <c r="D271" s="26" t="inlineStr">
         <is>
-          <t>Clackamas, Hood River</t>
+          <t>Grant, Wheeler</t>
         </is>
       </c>
       <c r="E271" s="25" t="inlineStr">
@@ -11729,32 +11731,32 @@
       </c>
       <c r="F271" s="25" t="inlineStr">
         <is>
-          <t>36%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G271" s="25" t="n">
-        <v>232</v>
+        <v>17</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="25" t="inlineStr">
         <is>
-          <t>97028</t>
+          <t>97750</t>
         </is>
       </c>
       <c r="B272" s="26" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>US-OR-WHE-WHH-060-A</t>
         </is>
       </c>
       <c r="C272" s="26" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Rowe Creek Complex</t>
         </is>
       </c>
       <c r="D272" s="26" t="inlineStr">
         <is>
-          <t>Clackamas, Hood River</t>
+          <t>Grant, Wheeler</t>
         </is>
       </c>
       <c r="E272" s="25" t="inlineStr">
@@ -11764,207 +11766,207 @@
       </c>
       <c r="F272" s="25" t="inlineStr">
         <is>
-          <t>89%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G272" s="25" t="n">
-        <v>38</v>
+        <v>13</v>
       </c>
     </row>
     <row r="273">
-      <c r="A273" s="23" t="inlineStr">
+      <c r="A273" s="25" t="inlineStr">
         <is>
           <t>97750</t>
         </is>
       </c>
-      <c r="B273" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-WHE-WHH-070</t>
-        </is>
-      </c>
-      <c r="C273" s="24" t="inlineStr">
+      <c r="B273" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-WHE-WHH-060-B</t>
+        </is>
+      </c>
+      <c r="C273" s="26" t="inlineStr">
         <is>
           <t>Rowe Creek Complex</t>
         </is>
       </c>
-      <c r="D273" s="24" t="inlineStr">
+      <c r="D273" s="26" t="inlineStr">
         <is>
           <t>Grant, Wheeler</t>
         </is>
       </c>
-      <c r="E273" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F273" s="23" t="inlineStr">
+      <c r="E273" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F273" s="25" t="inlineStr">
+        <is>
+          <t>86%</t>
+        </is>
+      </c>
+      <c r="G273" s="25" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="25" t="inlineStr">
+        <is>
+          <t>97750</t>
+        </is>
+      </c>
+      <c r="B274" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-WHE-WHH-054</t>
+        </is>
+      </c>
+      <c r="C274" s="26" t="inlineStr">
+        <is>
+          <t>Rowe Creek Complex</t>
+        </is>
+      </c>
+      <c r="D274" s="26" t="inlineStr">
+        <is>
+          <t>Grant, Wheeler</t>
+        </is>
+      </c>
+      <c r="E274" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F274" s="25" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="G274" s="25" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="25" t="inlineStr">
+        <is>
+          <t>97750</t>
+        </is>
+      </c>
+      <c r="B275" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-WHE-MIT-074</t>
+        </is>
+      </c>
+      <c r="C275" s="26" t="inlineStr">
+        <is>
+          <t>Rowe Creek Complex</t>
+        </is>
+      </c>
+      <c r="D275" s="26" t="inlineStr">
+        <is>
+          <t>Grant, Wheeler</t>
+        </is>
+      </c>
+      <c r="E275" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F275" s="25" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="G273" s="23" t="n">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" s="23" t="inlineStr">
+      <c r="G275" s="25" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="25" t="inlineStr">
         <is>
           <t>97750</t>
         </is>
       </c>
-      <c r="B274" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-WHE-WHH-068</t>
-        </is>
-      </c>
-      <c r="C274" s="24" t="inlineStr">
+      <c r="B276" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-WHE-MIT-078</t>
+        </is>
+      </c>
+      <c r="C276" s="26" t="inlineStr">
         <is>
           <t>Rowe Creek Complex</t>
         </is>
       </c>
-      <c r="D274" s="24" t="inlineStr">
+      <c r="D276" s="26" t="inlineStr">
         <is>
           <t>Grant, Wheeler</t>
         </is>
       </c>
-      <c r="E274" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F274" s="23" t="inlineStr">
+      <c r="E276" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F276" s="25" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="G274" s="23" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" s="23" t="inlineStr">
+      <c r="G276" s="25" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="25" t="inlineStr">
         <is>
           <t>97750</t>
         </is>
       </c>
-      <c r="B275" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-WHE-WHH-072-A</t>
-        </is>
-      </c>
-      <c r="C275" s="24" t="inlineStr">
-        <is>
-          <t>Rowe Creek Complex</t>
-        </is>
-      </c>
-      <c r="D275" s="24" t="inlineStr">
+      <c r="B277" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-GRA-GRN-115</t>
+        </is>
+      </c>
+      <c r="C277" s="26" t="inlineStr">
+        <is>
+          <t>Shingle</t>
+        </is>
+      </c>
+      <c r="D277" s="26" t="inlineStr">
         <is>
           <t>Grant, Wheeler</t>
         </is>
       </c>
-      <c r="E275" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F275" s="23" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G275" s="23" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" s="23" t="inlineStr">
-        <is>
-          <t>97750</t>
-        </is>
-      </c>
-      <c r="B276" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-WHE-WHH-034-A</t>
-        </is>
-      </c>
-      <c r="C276" s="24" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D276" s="24" t="inlineStr">
-        <is>
-          <t>Grant, Wheeler</t>
-        </is>
-      </c>
-      <c r="E276" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F276" s="23" t="inlineStr">
-        <is>
-          <t>69%</t>
-        </is>
-      </c>
-      <c r="G276" s="23" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" s="23" t="inlineStr">
-        <is>
-          <t>97750</t>
-        </is>
-      </c>
-      <c r="B277" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-WHE-WHH-072-C</t>
-        </is>
-      </c>
-      <c r="C277" s="24" t="inlineStr">
-        <is>
-          <t>Rowe Creek Complex</t>
-        </is>
-      </c>
-      <c r="D277" s="24" t="inlineStr">
-        <is>
-          <t>Grant, Wheeler</t>
-        </is>
-      </c>
-      <c r="E277" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F277" s="23" t="inlineStr">
-        <is>
-          <t>85%</t>
-        </is>
-      </c>
-      <c r="G277" s="23" t="n">
-        <v>4</v>
+      <c r="E277" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F277" s="25" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="G277" s="25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="23" t="inlineStr">
         <is>
-          <t>97750</t>
+          <t>97876</t>
         </is>
       </c>
       <c r="B278" s="24" t="inlineStr">
         <is>
-          <t>US-OR-WHE-WHH-090-A</t>
+          <t>US-OR-UNI-UCO-1435</t>
         </is>
       </c>
       <c r="C278" s="24" t="inlineStr">
         <is>
-          <t>Rowe Creek Complex</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D278" s="24" t="inlineStr">
         <is>
-          <t>Grant, Wheeler</t>
+          <t>Union</t>
         </is>
       </c>
       <c r="E278" s="23" t="inlineStr">
@@ -11974,67 +11976,67 @@
       </c>
       <c r="F278" s="23" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>74%</t>
         </is>
       </c>
       <c r="G278" s="23" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="23" t="inlineStr">
+        <is>
+          <t>97876</t>
+        </is>
+      </c>
+      <c r="B279" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-UNI-UCO-1450</t>
+        </is>
+      </c>
+      <c r="C279" s="24" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D279" s="24" t="inlineStr">
+        <is>
+          <t>Union</t>
+        </is>
+      </c>
+      <c r="E279" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F279" s="23" t="inlineStr">
+        <is>
+          <t>36%</t>
+        </is>
+      </c>
+      <c r="G279" s="23" t="n">
         <v>1</v>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" s="25" t="inlineStr">
-        <is>
-          <t>97750</t>
-        </is>
-      </c>
-      <c r="B279" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-WHE-MIT-076</t>
-        </is>
-      </c>
-      <c r="C279" s="26" t="inlineStr">
-        <is>
-          <t>Rowe Creek Complex</t>
-        </is>
-      </c>
-      <c r="D279" s="26" t="inlineStr">
-        <is>
-          <t>Grant, Wheeler</t>
-        </is>
-      </c>
-      <c r="E279" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F279" s="25" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G279" s="25" t="n">
-        <v>117</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="25" t="inlineStr">
         <is>
-          <t>97750</t>
+          <t>97876</t>
         </is>
       </c>
       <c r="B280" s="26" t="inlineStr">
         <is>
-          <t>US-OR-WHE-WHH-062</t>
+          <t>US-OR-UNI-UCO-1421</t>
         </is>
       </c>
       <c r="C280" s="26" t="inlineStr">
         <is>
-          <t>Rowe Creek Complex</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D280" s="26" t="inlineStr">
         <is>
-          <t>Grant, Wheeler</t>
+          <t>Union</t>
         </is>
       </c>
       <c r="E280" s="25" t="inlineStr">
@@ -12048,28 +12050,28 @@
         </is>
       </c>
       <c r="G280" s="25" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="25" t="inlineStr">
         <is>
-          <t>97750</t>
+          <t>97876</t>
         </is>
       </c>
       <c r="B281" s="26" t="inlineStr">
         <is>
-          <t>US-OR-WHE-WHH-060-A</t>
+          <t>US-OR-UNI-UCO-1436</t>
         </is>
       </c>
       <c r="C281" s="26" t="inlineStr">
         <is>
-          <t>Rowe Creek Complex</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D281" s="26" t="inlineStr">
         <is>
-          <t>Grant, Wheeler</t>
+          <t>Union</t>
         </is>
       </c>
       <c r="E281" s="25" t="inlineStr">
@@ -12083,28 +12085,28 @@
         </is>
       </c>
       <c r="G281" s="25" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="25" t="inlineStr">
         <is>
-          <t>97750</t>
+          <t>97876</t>
         </is>
       </c>
       <c r="B282" s="26" t="inlineStr">
         <is>
-          <t>US-OR-WHE-WHH-060-B</t>
+          <t>US-OR-UNI-UCO-1437</t>
         </is>
       </c>
       <c r="C282" s="26" t="inlineStr">
         <is>
-          <t>Rowe Creek Complex</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D282" s="26" t="inlineStr">
         <is>
-          <t>Grant, Wheeler</t>
+          <t>Union</t>
         </is>
       </c>
       <c r="E282" s="25" t="inlineStr">
@@ -12114,32 +12116,32 @@
       </c>
       <c r="F282" s="25" t="inlineStr">
         <is>
-          <t>86%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G282" s="25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="25" t="inlineStr">
         <is>
-          <t>97750</t>
+          <t>97876</t>
         </is>
       </c>
       <c r="B283" s="26" t="inlineStr">
         <is>
-          <t>US-OR-WHE-WHH-054</t>
+          <t>US-OR-UNI-UCO-1438</t>
         </is>
       </c>
       <c r="C283" s="26" t="inlineStr">
         <is>
-          <t>Rowe Creek Complex</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D283" s="26" t="inlineStr">
         <is>
-          <t>Grant, Wheeler</t>
+          <t>Union</t>
         </is>
       </c>
       <c r="E283" s="25" t="inlineStr">
@@ -12149,102 +12151,102 @@
       </c>
       <c r="F283" s="25" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>99%</t>
         </is>
       </c>
       <c r="G283" s="25" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="284">
-      <c r="A284" s="25" t="inlineStr">
-        <is>
-          <t>97750</t>
-        </is>
-      </c>
-      <c r="B284" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-WHE-MIT-074</t>
-        </is>
-      </c>
-      <c r="C284" s="26" t="inlineStr">
-        <is>
-          <t>Rowe Creek Complex</t>
-        </is>
-      </c>
-      <c r="D284" s="26" t="inlineStr">
-        <is>
-          <t>Grant, Wheeler</t>
-        </is>
-      </c>
-      <c r="E284" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F284" s="25" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G284" s="25" t="n">
-        <v>5</v>
+      <c r="A284" s="23" t="inlineStr">
+        <is>
+          <t>97621</t>
+        </is>
+      </c>
+      <c r="B284" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-KLA-KLA-1572</t>
+        </is>
+      </c>
+      <c r="C284" s="24" t="inlineStr">
+        <is>
+          <t>Wrights Spring</t>
+        </is>
+      </c>
+      <c r="D284" s="24" t="inlineStr">
+        <is>
+          <t>Klamath</t>
+        </is>
+      </c>
+      <c r="E284" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F284" s="23" t="inlineStr">
+        <is>
+          <t>31%</t>
+        </is>
+      </c>
+      <c r="G284" s="23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="285">
-      <c r="A285" s="25" t="inlineStr">
-        <is>
-          <t>97750</t>
-        </is>
-      </c>
-      <c r="B285" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-WHE-MIT-078</t>
-        </is>
-      </c>
-      <c r="C285" s="26" t="inlineStr">
-        <is>
-          <t>Rowe Creek Complex</t>
-        </is>
-      </c>
-      <c r="D285" s="26" t="inlineStr">
-        <is>
-          <t>Grant, Wheeler</t>
-        </is>
-      </c>
-      <c r="E285" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F285" s="25" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G285" s="25" t="n">
-        <v>4</v>
+      <c r="A285" s="23" t="inlineStr">
+        <is>
+          <t>97621</t>
+        </is>
+      </c>
+      <c r="B285" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-KLA-KLA-1566</t>
+        </is>
+      </c>
+      <c r="C285" s="24" t="inlineStr">
+        <is>
+          <t>Wrights Spring</t>
+        </is>
+      </c>
+      <c r="D285" s="24" t="inlineStr">
+        <is>
+          <t>Klamath</t>
+        </is>
+      </c>
+      <c r="E285" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F285" s="23" t="inlineStr">
+        <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="G285" s="23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="25" t="inlineStr">
         <is>
-          <t>97750</t>
+          <t>97621</t>
         </is>
       </c>
       <c r="B286" s="26" t="inlineStr">
         <is>
-          <t>US-OR-GRA-GRN-115</t>
+          <t>US-OR-KLA-KLA-1471</t>
         </is>
       </c>
       <c r="C286" s="26" t="inlineStr">
         <is>
-          <t>Shingle</t>
+          <t>Wrights Spring</t>
         </is>
       </c>
       <c r="D286" s="26" t="inlineStr">
         <is>
-          <t>Grant, Wheeler</t>
+          <t>Klamath</t>
         </is>
       </c>
       <c r="E286" s="25" t="inlineStr">
@@ -12254,102 +12256,102 @@
       </c>
       <c r="F286" s="25" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G286" s="25" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="287">
-      <c r="A287" s="23" t="inlineStr">
-        <is>
-          <t>97876</t>
-        </is>
-      </c>
-      <c r="B287" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-UNI-UCO-1435</t>
-        </is>
-      </c>
-      <c r="C287" s="24" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D287" s="24" t="inlineStr">
-        <is>
-          <t>Union</t>
-        </is>
-      </c>
-      <c r="E287" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F287" s="23" t="inlineStr">
-        <is>
-          <t>74%</t>
-        </is>
-      </c>
-      <c r="G287" s="23" t="n">
-        <v>6</v>
+      <c r="A287" s="25" t="inlineStr">
+        <is>
+          <t>97621</t>
+        </is>
+      </c>
+      <c r="B287" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-KLA-KLA-1586</t>
+        </is>
+      </c>
+      <c r="C287" s="26" t="inlineStr">
+        <is>
+          <t>Wrights Spring</t>
+        </is>
+      </c>
+      <c r="D287" s="26" t="inlineStr">
+        <is>
+          <t>Klamath</t>
+        </is>
+      </c>
+      <c r="E287" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F287" s="25" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G287" s="25" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="288">
-      <c r="A288" s="23" t="inlineStr">
-        <is>
-          <t>97876</t>
-        </is>
-      </c>
-      <c r="B288" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-UNI-UCO-1450</t>
-        </is>
-      </c>
-      <c r="C288" s="24" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D288" s="24" t="inlineStr">
-        <is>
-          <t>Union</t>
-        </is>
-      </c>
-      <c r="E288" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F288" s="23" t="inlineStr">
-        <is>
-          <t>36%</t>
-        </is>
-      </c>
-      <c r="G288" s="23" t="n">
-        <v>1</v>
+      <c r="A288" s="25" t="inlineStr">
+        <is>
+          <t>97621</t>
+        </is>
+      </c>
+      <c r="B288" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-KLA-FHZ-1584-A</t>
+        </is>
+      </c>
+      <c r="C288" s="26" t="inlineStr">
+        <is>
+          <t>Wrights Spring</t>
+        </is>
+      </c>
+      <c r="D288" s="26" t="inlineStr">
+        <is>
+          <t>Klamath</t>
+        </is>
+      </c>
+      <c r="E288" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F288" s="25" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="G288" s="25" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="25" t="inlineStr">
         <is>
-          <t>97876</t>
+          <t>97621</t>
         </is>
       </c>
       <c r="B289" s="26" t="inlineStr">
         <is>
-          <t>US-OR-UNI-UCO-1421</t>
+          <t>US-OR-KLA-KLA-1472</t>
         </is>
       </c>
       <c r="C289" s="26" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Wrights Spring</t>
         </is>
       </c>
       <c r="D289" s="26" t="inlineStr">
         <is>
-          <t>Union</t>
+          <t>Klamath</t>
         </is>
       </c>
       <c r="E289" s="25" t="inlineStr">
@@ -12359,32 +12361,32 @@
       </c>
       <c r="F289" s="25" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>93%</t>
         </is>
       </c>
       <c r="G289" s="25" t="n">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="25" t="inlineStr">
         <is>
-          <t>97876</t>
+          <t>97621</t>
         </is>
       </c>
       <c r="B290" s="26" t="inlineStr">
         <is>
-          <t>US-OR-UNI-UCO-1436</t>
+          <t>US-OR-KLA-KLA-1452</t>
         </is>
       </c>
       <c r="C290" s="26" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Wrights Spring</t>
         </is>
       </c>
       <c r="D290" s="26" t="inlineStr">
         <is>
-          <t>Union</t>
+          <t>Klamath</t>
         </is>
       </c>
       <c r="E290" s="25" t="inlineStr">
@@ -12394,32 +12396,32 @@
       </c>
       <c r="F290" s="25" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="G290" s="25" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="25" t="inlineStr">
         <is>
-          <t>97876</t>
+          <t>97621</t>
         </is>
       </c>
       <c r="B291" s="26" t="inlineStr">
         <is>
-          <t>US-OR-UNI-UCO-1437</t>
+          <t>US-OR-KLA-FHZ-1585</t>
         </is>
       </c>
       <c r="C291" s="26" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Wrights Spring</t>
         </is>
       </c>
       <c r="D291" s="26" t="inlineStr">
         <is>
-          <t>Union</t>
+          <t>Klamath</t>
         </is>
       </c>
       <c r="E291" s="25" t="inlineStr">
@@ -12429,32 +12431,32 @@
       </c>
       <c r="F291" s="25" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="G291" s="25" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="25" t="inlineStr">
         <is>
-          <t>97876</t>
+          <t>97621</t>
         </is>
       </c>
       <c r="B292" s="26" t="inlineStr">
         <is>
-          <t>US-OR-UNI-UCO-1438</t>
+          <t>US-OR-KLA-FHZ-1584-B</t>
         </is>
       </c>
       <c r="C292" s="26" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Wrights Spring</t>
         </is>
       </c>
       <c r="D292" s="26" t="inlineStr">
         <is>
-          <t>Union</t>
+          <t>Klamath</t>
         </is>
       </c>
       <c r="E292" s="25" t="inlineStr">
@@ -12464,11 +12466,11 @@
       </c>
       <c r="F292" s="25" t="inlineStr">
         <is>
-          <t>99%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G292" s="25" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="293">
@@ -14899,7 +14901,7 @@
       </c>
       <c r="C362" s="26" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Fielders Mountain</t>
         </is>
       </c>
       <c r="D362" s="26" t="inlineStr">
@@ -14934,7 +14936,7 @@
       </c>
       <c r="C363" s="26" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Fielders Mountain</t>
         </is>
       </c>
       <c r="D363" s="26" t="inlineStr">
@@ -15004,7 +15006,7 @@
       </c>
       <c r="C365" s="26" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Fielders Mountain</t>
         </is>
       </c>
       <c r="D365" s="26" t="inlineStr">
@@ -15039,7 +15041,7 @@
       </c>
       <c r="C366" s="26" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Fielders Mountain</t>
         </is>
       </c>
       <c r="D366" s="26" t="inlineStr">
